--- a/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE4E833-7F61-4C6E-8D15-45880EDD1F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96801450-6965-400D-B623-6761E905D9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="09.02" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="14.02" sheetId="6" r:id="rId6"/>
     <sheet name="15.02" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'09.02'!$A$1:$I$102</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="178">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -437,12 +440,167 @@
   <si>
     <t xml:space="preserve">ALECIO ANTUNES MACEDO                        </t>
   </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>GABRIEL ALAMINO SABIO FILHO CPF 1532488823</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 09.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE VIEIRA DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARISA ANTUNES LINCOLN DE GODOY MORONI       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO KENDI TATENO                        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: HODOMETRO (FOTO NAO ENQUADRADA CORRETAMENTE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO CRISTONI DE MENDONCA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHELLE GOMES CALDAS DE SA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO. FOTO INCORRETA: CHASSI. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JENIFER ADRIANE BASTOS                       </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO: tipo de documento errado enviado sem prazo para solicitar correção.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJAINE MENDES DA CUNHA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACQUELINE GOULART BRUZEGUINI                </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 09.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEVATO MARCENARIA LTDA ME                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR PEDOTE DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELLY CRISTIANE LOURENCO DA SILVA            </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM CARRO LIGADO (VEICULO DESLIGADO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO ANTONIO DE PAIVA                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO SEGURADO NÃO REFEZ OS PASSOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODOLFO CARVALHO CORREA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIEIRA ACO INDUSTRIA COMERCIO LTDA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO CESAR PINHEIRO SALLES                  </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Lateral direita (Não tirou foto do passo), Painel com a motocicleta ligada (Veiculo desligado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA LIVIO ZANE                         </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve quebra de vigência de 49 dias e não houve sinistr
+o , conforme regra mantem a classe de bônus, assim sendo o correto
+bônus0.
+Com a correção ficou 10x R$ 191,94. Podemos emitir d
+esta forma?</t>
+  </si>
+  <si>
+    <t>CASA DOS MANTOS VESTUARIO E ACESSORIOS LTDA M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAN DE SOUZA                              </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAURICIO SPAGNOL                             </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) MAURICIO SPAGNOL, pois este não consta como condutor na apólic
+e anterior.
+Neste caso estamos nesta data efetuando a recusa
+desta proposta. Orientamos transmitir um novo processo como Seguro
+Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOMINGOS TERTULINO DA SILVA JUNIOR ME        </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Documento da moto, Número do Chassi /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ KELWER GRAMINHA SILVA                   </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Chassi, Documento do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO ARI JUNIOR DE PAIVA ME             </t>
+  </si>
+  <si>
+    <t>*PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFERSON CARLOS DE OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGIO DA SILVA                               </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CRLV, PAINEL. OBS: KM PARCIAL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO MARCOS DE LARA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZILMA SILVA VIEIRA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO ZANFOLIM GARCIA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO SEBASTIAO FROEZ GOMES DOS SANTOS     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMANUELLA CERVEIRA DE ANDRADE CUNHA          </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,8 +637,14 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,8 +657,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -717,9 +887,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -731,7 +923,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,9 +1054,6 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -877,13 +1066,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -910,34 +1093,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1275,9 +1486,9 @@
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="6" max="6" width="46.42578125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1320,16 +1531,16 @@
       <c r="C2" s="25">
         <v>46062</v>
       </c>
-      <c r="D2" s="73">
+      <c r="D2" s="22">
         <v>136458414</v>
       </c>
       <c r="E2" s="17">
         <v>3450233512</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="G2" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="45" t="s">
@@ -1349,16 +1560,16 @@
       <c r="C3" s="25">
         <v>46062</v>
       </c>
-      <c r="D3" s="73">
+      <c r="D3" s="22">
         <v>136465260</v>
       </c>
       <c r="E3" s="17">
         <v>3450232929</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="45" t="s">
@@ -1378,16 +1589,16 @@
       <c r="C4" s="25">
         <v>46062</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="22">
         <v>136471203</v>
       </c>
       <c r="E4" s="17">
         <v>3450234513</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="71" t="s">
+      <c r="G4" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="45" t="s">
@@ -1407,16 +1618,16 @@
       <c r="C5" s="25">
         <v>46062</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="22">
         <v>136473444</v>
       </c>
       <c r="E5" s="17">
         <v>3450234733</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1436,16 +1647,16 @@
       <c r="C6" s="25">
         <v>46062</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="22">
         <v>136458429</v>
       </c>
       <c r="E6" s="17">
         <v>3450233523</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1465,16 +1676,16 @@
       <c r="C7" s="25">
         <v>46062</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="22">
         <v>136461389</v>
       </c>
       <c r="E7" s="17">
         <v>3450233721</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="71" t="s">
+      <c r="G7" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="45" t="s">
@@ -1494,16 +1705,16 @@
       <c r="C8" s="25">
         <v>46062</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="22">
         <v>136474453</v>
       </c>
       <c r="E8" s="17">
         <v>3450234832</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -1523,16 +1734,16 @@
       <c r="C9" s="25">
         <v>46062</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="22">
         <v>136475756</v>
       </c>
       <c r="E9" s="17">
         <v>3450234909</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1552,16 +1763,16 @@
       <c r="C10" s="25">
         <v>46062</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="22">
         <v>136472176</v>
       </c>
       <c r="E10" s="17">
         <v>3450234601</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1581,16 +1792,16 @@
       <c r="C11" s="25">
         <v>46062</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="22">
         <v>136482435</v>
       </c>
       <c r="E11" s="17">
         <v>3450235239</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="71" t="s">
+      <c r="G11" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1610,16 +1821,16 @@
       <c r="C12" s="25">
         <v>46062</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="22">
         <v>136482788</v>
       </c>
       <c r="E12" s="17">
         <v>3450235316</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="71" t="s">
+      <c r="G12" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1639,16 +1850,16 @@
       <c r="C13" s="25">
         <v>46062</v>
       </c>
-      <c r="D13" s="73">
+      <c r="D13" s="22">
         <v>136492609</v>
       </c>
       <c r="E13" s="17">
         <v>3450236240</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="71" t="s">
+      <c r="G13" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="45" t="s">
@@ -1668,16 +1879,16 @@
       <c r="C14" s="25">
         <v>46062</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="22">
         <v>136493802</v>
       </c>
       <c r="E14" s="17">
         <v>3450236394</v>
       </c>
-      <c r="F14" s="70" t="s">
+      <c r="F14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="71" t="s">
+      <c r="G14" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="45" t="s">
@@ -1697,16 +1908,16 @@
       <c r="C15" s="25">
         <v>46062</v>
       </c>
-      <c r="D15" s="73">
+      <c r="D15" s="22">
         <v>136492072</v>
       </c>
       <c r="E15" s="17">
         <v>3450236196</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="71" t="s">
+      <c r="G15" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H15" s="45" t="s">
@@ -1726,16 +1937,16 @@
       <c r="C16" s="25">
         <v>46062</v>
       </c>
-      <c r="D16" s="73">
+      <c r="D16" s="22">
         <v>136493898</v>
       </c>
       <c r="E16" s="17">
         <v>3450236449</v>
       </c>
-      <c r="F16" s="70" t="s">
+      <c r="F16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="71" t="s">
+      <c r="G16" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="45" t="s">
@@ -1755,16 +1966,16 @@
       <c r="C17" s="25">
         <v>46062</v>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="22">
         <v>136495966</v>
       </c>
       <c r="E17" s="17">
         <v>3450236691</v>
       </c>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="71" t="s">
+      <c r="G17" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H17" s="45" t="s">
@@ -1784,16 +1995,16 @@
       <c r="C18" s="25">
         <v>46062</v>
       </c>
-      <c r="D18" s="73">
+      <c r="D18" s="22">
         <v>136494395</v>
       </c>
       <c r="E18" s="17">
         <v>3450236515</v>
       </c>
-      <c r="F18" s="70" t="s">
+      <c r="F18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="71" t="s">
+      <c r="G18" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="45" t="s">
@@ -1813,16 +2024,16 @@
       <c r="C19" s="25">
         <v>46062</v>
       </c>
-      <c r="D19" s="73">
+      <c r="D19" s="22">
         <v>136497331</v>
       </c>
       <c r="E19" s="17">
         <v>3450236823</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="71" t="s">
+      <c r="G19" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="45" t="s">
@@ -1842,16 +2053,16 @@
       <c r="C20" s="25">
         <v>46062</v>
       </c>
-      <c r="D20" s="73">
+      <c r="D20" s="22">
         <v>136496525</v>
       </c>
       <c r="E20" s="17">
         <v>3450236801</v>
       </c>
-      <c r="F20" s="70" t="s">
+      <c r="F20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="71" t="s">
+      <c r="G20" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="45" t="s">
@@ -1871,16 +2082,16 @@
       <c r="C21" s="25">
         <v>46062</v>
       </c>
-      <c r="D21" s="73">
+      <c r="D21" s="22">
         <v>136478940</v>
       </c>
       <c r="E21" s="17">
         <v>3450234964</v>
       </c>
-      <c r="F21" s="70" t="s">
+      <c r="F21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="71" t="s">
+      <c r="G21" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="45" t="s">
@@ -1900,16 +2111,16 @@
       <c r="C22" s="25">
         <v>46062</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D22" s="22">
         <v>136484224</v>
       </c>
       <c r="E22" s="17">
         <v>3450235503</v>
       </c>
-      <c r="F22" s="70" t="s">
+      <c r="F22" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="71" t="s">
+      <c r="G22" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="45" t="s">
@@ -1929,16 +2140,16 @@
       <c r="C23" s="25">
         <v>46062</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D23" s="22">
         <v>136495664</v>
       </c>
       <c r="E23" s="17">
         <v>3450236658</v>
       </c>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="71" t="s">
+      <c r="G23" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H23" s="45" t="s">
@@ -1958,16 +2169,16 @@
       <c r="C24" s="25">
         <v>46062</v>
       </c>
-      <c r="D24" s="73">
+      <c r="D24" s="22">
         <v>136517042</v>
       </c>
       <c r="E24" s="17">
         <v>3450237934</v>
       </c>
-      <c r="F24" s="70" t="s">
+      <c r="F24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="71" t="s">
+      <c r="G24" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -1987,16 +2198,16 @@
       <c r="C25" s="25">
         <v>46062</v>
       </c>
-      <c r="D25" s="73">
+      <c r="D25" s="22">
         <v>136507603</v>
       </c>
       <c r="E25" s="17">
         <v>3450237318</v>
       </c>
-      <c r="F25" s="70" t="s">
+      <c r="F25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="71" t="s">
+      <c r="G25" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H25" s="45" t="s">
@@ -2016,16 +2227,16 @@
       <c r="C26" s="25">
         <v>46062</v>
       </c>
-      <c r="D26" s="73">
+      <c r="D26" s="22">
         <v>136529840</v>
       </c>
       <c r="E26" s="17">
         <v>3450238870</v>
       </c>
-      <c r="F26" s="70" t="s">
+      <c r="F26" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="71" t="s">
+      <c r="G26" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H26" s="45" t="s">
@@ -2045,16 +2256,16 @@
       <c r="C27" s="25">
         <v>46062</v>
       </c>
-      <c r="D27" s="73">
+      <c r="D27" s="22">
         <v>136532121</v>
       </c>
       <c r="E27" s="17">
         <v>3450239045</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="71" t="s">
+      <c r="G27" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H27" s="45" t="s">
@@ -2074,16 +2285,16 @@
       <c r="C28" s="25">
         <v>46062</v>
       </c>
-      <c r="D28" s="73">
+      <c r="D28" s="22">
         <v>136530866</v>
       </c>
       <c r="E28" s="17">
         <v>3450238968</v>
       </c>
-      <c r="F28" s="70" t="s">
+      <c r="F28" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="71" t="s">
+      <c r="G28" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H28" s="45" t="s">
@@ -2103,16 +2314,16 @@
       <c r="C29" s="25">
         <v>46062</v>
       </c>
-      <c r="D29" s="73">
+      <c r="D29" s="22">
         <v>136537723</v>
       </c>
       <c r="E29" s="17">
         <v>3450239628</v>
       </c>
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="71" t="s">
+      <c r="G29" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="45" t="s">
@@ -2132,16 +2343,16 @@
       <c r="C30" s="25">
         <v>46062</v>
       </c>
-      <c r="D30" s="73">
+      <c r="D30" s="22">
         <v>136530551</v>
       </c>
       <c r="E30" s="17">
         <v>3450238935</v>
       </c>
-      <c r="F30" s="70" t="s">
+      <c r="F30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="71" t="s">
+      <c r="G30" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H30" s="45" t="s">
@@ -2161,16 +2372,16 @@
       <c r="C31" s="25">
         <v>46062</v>
       </c>
-      <c r="D31" s="73">
+      <c r="D31" s="22">
         <v>136532327</v>
       </c>
       <c r="E31" s="17">
         <v>3450239089</v>
       </c>
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="71" t="s">
+      <c r="G31" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H31" s="45" t="s">
@@ -2190,16 +2401,16 @@
       <c r="C32" s="25">
         <v>46062</v>
       </c>
-      <c r="D32" s="73">
+      <c r="D32" s="22">
         <v>136473711</v>
       </c>
       <c r="E32" s="17">
         <v>3450234755</v>
       </c>
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="71" t="s">
+      <c r="G32" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="45" t="s">
@@ -2219,16 +2430,16 @@
       <c r="C33" s="25">
         <v>46062</v>
       </c>
-      <c r="D33" s="73">
+      <c r="D33" s="22">
         <v>136528085</v>
       </c>
       <c r="E33" s="17">
         <v>3450238715</v>
       </c>
-      <c r="F33" s="70" t="s">
+      <c r="F33" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G33" s="71" t="s">
+      <c r="G33" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H33" s="45" t="s">
@@ -2248,16 +2459,16 @@
       <c r="C34" s="25">
         <v>46062</v>
       </c>
-      <c r="D34" s="73">
+      <c r="D34" s="22">
         <v>136483835</v>
       </c>
       <c r="E34" s="17">
         <v>3450235437</v>
       </c>
-      <c r="F34" s="70" t="s">
+      <c r="F34" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="71" t="s">
+      <c r="G34" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H34" s="45" t="s">
@@ -2277,16 +2488,16 @@
       <c r="C35" s="25">
         <v>46062</v>
       </c>
-      <c r="D35" s="73">
+      <c r="D35" s="22">
         <v>136485047</v>
       </c>
       <c r="E35" s="17">
         <v>3450235624</v>
       </c>
-      <c r="F35" s="70" t="s">
+      <c r="F35" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="71" t="s">
+      <c r="G35" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H35" s="45" t="s">
@@ -2306,16 +2517,16 @@
       <c r="C36" s="25">
         <v>46062</v>
       </c>
-      <c r="D36" s="73">
+      <c r="D36" s="22">
         <v>136570165</v>
       </c>
       <c r="E36" s="17">
         <v>3450241828</v>
       </c>
-      <c r="F36" s="70" t="s">
+      <c r="F36" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G36" s="71" t="s">
+      <c r="G36" s="67" t="s">
         <v>55</v>
       </c>
       <c r="H36" s="45" t="s">
@@ -2335,16 +2546,16 @@
       <c r="C37" s="25">
         <v>46062</v>
       </c>
-      <c r="D37" s="73">
+      <c r="D37" s="22">
         <v>136576941</v>
       </c>
       <c r="E37" s="17">
         <v>3450242830</v>
       </c>
-      <c r="F37" s="70" t="s">
+      <c r="F37" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="71" t="s">
+      <c r="G37" s="67" t="s">
         <v>55</v>
       </c>
       <c r="H37" s="45" t="s">
@@ -2364,16 +2575,16 @@
       <c r="C38" s="25">
         <v>46062</v>
       </c>
-      <c r="D38" s="73">
+      <c r="D38" s="22">
         <v>136522475</v>
       </c>
       <c r="E38" s="17">
         <v>3450238176</v>
       </c>
-      <c r="F38" s="70" t="s">
+      <c r="F38" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="71" t="s">
+      <c r="G38" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H38" s="45" t="s">
@@ -2393,16 +2604,16 @@
       <c r="C39" s="25">
         <v>46062</v>
       </c>
-      <c r="D39" s="73">
+      <c r="D39" s="22">
         <v>136572095</v>
       </c>
       <c r="E39" s="17">
         <v>3450242224</v>
       </c>
-      <c r="F39" s="70" t="s">
+      <c r="F39" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="71" t="s">
+      <c r="G39" s="67" t="s">
         <v>61</v>
       </c>
       <c r="H39" s="46" t="s">
@@ -2422,16 +2633,16 @@
       <c r="C40" s="25">
         <v>46062</v>
       </c>
-      <c r="D40" s="73">
+      <c r="D40" s="22">
         <v>136496014</v>
       </c>
       <c r="E40" s="17">
         <v>3450236702</v>
       </c>
-      <c r="F40" s="70" t="s">
+      <c r="F40" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="71" t="s">
+      <c r="G40" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="46" t="s">
@@ -2451,16 +2662,16 @@
       <c r="C41" s="25">
         <v>46062</v>
       </c>
-      <c r="D41" s="73">
+      <c r="D41" s="22">
         <v>136510993</v>
       </c>
       <c r="E41" s="17">
         <v>3450237472</v>
       </c>
-      <c r="F41" s="70" t="s">
+      <c r="F41" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G41" s="71" t="s">
+      <c r="G41" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H41" s="46" t="s">
@@ -2480,16 +2691,16 @@
       <c r="C42" s="25">
         <v>46062</v>
       </c>
-      <c r="D42" s="73">
+      <c r="D42" s="22">
         <v>136445487</v>
       </c>
       <c r="E42" s="17">
         <v>3450232445</v>
       </c>
-      <c r="F42" s="70" t="s">
+      <c r="F42" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="71" t="s">
+      <c r="G42" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="46" t="s">
@@ -2509,16 +2720,16 @@
       <c r="C43" s="25">
         <v>46062</v>
       </c>
-      <c r="D43" s="73">
+      <c r="D43" s="22">
         <v>136448051</v>
       </c>
       <c r="E43" s="17">
         <v>3450232753</v>
       </c>
-      <c r="F43" s="70" t="s">
+      <c r="F43" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G43" s="71" t="s">
+      <c r="G43" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="46" t="s">
@@ -2538,16 +2749,16 @@
       <c r="C44" s="25">
         <v>46062</v>
       </c>
-      <c r="D44" s="73">
+      <c r="D44" s="22">
         <v>136440998</v>
       </c>
       <c r="E44" s="17">
         <v>3450230740</v>
       </c>
-      <c r="F44" s="70" t="s">
+      <c r="F44" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="71" t="s">
+      <c r="G44" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="46" t="s">
@@ -2567,16 +2778,16 @@
       <c r="C45" s="25">
         <v>46062</v>
       </c>
-      <c r="D45" s="73">
+      <c r="D45" s="22">
         <v>136448132</v>
       </c>
       <c r="E45" s="17">
         <v>3450232786</v>
       </c>
-      <c r="F45" s="70" t="s">
+      <c r="F45" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G45" s="71" t="s">
+      <c r="G45" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="46" t="s">
@@ -2596,16 +2807,16 @@
       <c r="C46" s="25">
         <v>46062</v>
       </c>
-      <c r="D46" s="73">
+      <c r="D46" s="22">
         <v>136448415</v>
       </c>
       <c r="E46" s="17">
         <v>3450232820</v>
       </c>
-      <c r="F46" s="70" t="s">
+      <c r="F46" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="71" t="s">
+      <c r="G46" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="46" t="s">
@@ -2625,19 +2836,19 @@
       <c r="C47" s="25">
         <v>46062</v>
       </c>
-      <c r="D47" s="73">
+      <c r="D47" s="22">
         <v>136453329</v>
       </c>
       <c r="E47" s="17">
         <v>3450233303</v>
       </c>
-      <c r="F47" s="70" t="s">
+      <c r="F47" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="71" t="s">
+      <c r="G47" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="74" t="s">
+      <c r="H47" s="46" t="s">
         <v>72</v>
       </c>
       <c r="I47" s="44">
@@ -2654,16 +2865,16 @@
       <c r="C48" s="25">
         <v>46062</v>
       </c>
-      <c r="D48" s="73">
+      <c r="D48" s="22">
         <v>136446494</v>
       </c>
       <c r="E48" s="17">
         <v>3450232621</v>
       </c>
-      <c r="F48" s="70" t="s">
+      <c r="F48" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G48" s="71" t="s">
+      <c r="G48" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H48" s="46" t="s">
@@ -2683,16 +2894,16 @@
       <c r="C49" s="25">
         <v>46062</v>
       </c>
-      <c r="D49" s="73">
+      <c r="D49" s="22">
         <v>136448763</v>
       </c>
       <c r="E49" s="17">
         <v>3450232874</v>
       </c>
-      <c r="F49" s="70" t="s">
+      <c r="F49" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G49" s="71" t="s">
+      <c r="G49" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H49" s="46" t="s">
@@ -2712,16 +2923,16 @@
       <c r="C50" s="25">
         <v>46062</v>
       </c>
-      <c r="D50" s="73">
+      <c r="D50" s="22">
         <v>136443035</v>
       </c>
       <c r="E50" s="17">
         <v>3450232302</v>
       </c>
-      <c r="F50" s="70" t="s">
+      <c r="F50" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G50" s="71" t="s">
+      <c r="G50" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H50" s="46" t="s">
@@ -2741,16 +2952,16 @@
       <c r="C51" s="25">
         <v>46062</v>
       </c>
-      <c r="D51" s="73">
+      <c r="D51" s="22">
         <v>136449209</v>
       </c>
       <c r="E51" s="17">
         <v>3450232896</v>
       </c>
-      <c r="F51" s="70" t="s">
+      <c r="F51" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G51" s="71" t="s">
+      <c r="G51" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H51" s="46" t="s">
@@ -2770,16 +2981,16 @@
       <c r="C52" s="25">
         <v>46062</v>
       </c>
-      <c r="D52" s="73">
+      <c r="D52" s="22">
         <v>136450518</v>
       </c>
       <c r="E52" s="17">
         <v>3450233040</v>
       </c>
-      <c r="F52" s="70" t="s">
+      <c r="F52" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G52" s="71" t="s">
+      <c r="G52" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H52" s="46" t="s">
@@ -2799,16 +3010,16 @@
       <c r="C53" s="25">
         <v>46062</v>
       </c>
-      <c r="D53" s="73">
+      <c r="D53" s="22">
         <v>136451363</v>
       </c>
       <c r="E53" s="17">
         <v>3450233083</v>
       </c>
-      <c r="F53" s="70" t="s">
+      <c r="F53" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G53" s="71" t="s">
+      <c r="G53" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H53" s="46" t="s">
@@ -2828,16 +3039,16 @@
       <c r="C54" s="25">
         <v>46062</v>
       </c>
-      <c r="D54" s="73">
+      <c r="D54" s="22">
         <v>136451835</v>
       </c>
       <c r="E54" s="17">
         <v>3450233171</v>
       </c>
-      <c r="F54" s="70" t="s">
+      <c r="F54" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G54" s="71" t="s">
+      <c r="G54" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H54" s="46" t="s">
@@ -2857,16 +3068,16 @@
       <c r="C55" s="25">
         <v>46062</v>
       </c>
-      <c r="D55" s="73">
+      <c r="D55" s="22">
         <v>136439942</v>
       </c>
       <c r="E55" s="17">
         <v>3450231389</v>
       </c>
-      <c r="F55" s="70" t="s">
+      <c r="F55" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G55" s="71" t="s">
+      <c r="G55" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H55" s="46" t="s">
@@ -2886,16 +3097,16 @@
       <c r="C56" s="25">
         <v>46062</v>
       </c>
-      <c r="D56" s="73">
+      <c r="D56" s="22">
         <v>136448511</v>
       </c>
       <c r="E56" s="17">
         <v>3450232830</v>
       </c>
-      <c r="F56" s="70" t="s">
+      <c r="F56" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G56" s="71" t="s">
+      <c r="G56" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H56" s="46" t="s">
@@ -2915,16 +3126,16 @@
       <c r="C57" s="25">
         <v>46062</v>
       </c>
-      <c r="D57" s="73">
+      <c r="D57" s="22">
         <v>136440268</v>
       </c>
       <c r="E57" s="17">
         <v>3450231213</v>
       </c>
-      <c r="F57" s="70" t="s">
+      <c r="F57" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G57" s="71" t="s">
+      <c r="G57" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H57" s="46" t="s">
@@ -2944,16 +3155,16 @@
       <c r="C58" s="25">
         <v>46062</v>
       </c>
-      <c r="D58" s="73">
+      <c r="D58" s="22">
         <v>136454528</v>
       </c>
       <c r="E58" s="17">
         <v>3450233391</v>
       </c>
-      <c r="F58" s="70" t="s">
+      <c r="F58" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G58" s="71" t="s">
+      <c r="G58" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H58" s="46" t="s">
@@ -2973,16 +3184,16 @@
       <c r="C59" s="25">
         <v>46062</v>
       </c>
-      <c r="D59" s="73">
+      <c r="D59" s="22">
         <v>136438866</v>
       </c>
       <c r="E59" s="17">
         <v>3450231587</v>
       </c>
-      <c r="F59" s="70" t="s">
+      <c r="F59" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G59" s="71" t="s">
+      <c r="G59" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H59" s="46" t="s">
@@ -3002,16 +3213,16 @@
       <c r="C60" s="25">
         <v>46062</v>
       </c>
-      <c r="D60" s="73">
+      <c r="D60" s="22">
         <v>136446064</v>
       </c>
       <c r="E60" s="17">
         <v>3450232577</v>
       </c>
-      <c r="F60" s="70" t="s">
+      <c r="F60" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G60" s="71" t="s">
+      <c r="G60" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H60" s="46" t="s">
@@ -3031,16 +3242,16 @@
       <c r="C61" s="25">
         <v>46062</v>
       </c>
-      <c r="D61" s="73">
+      <c r="D61" s="22">
         <v>136446666</v>
       </c>
       <c r="E61" s="17">
         <v>3450232654</v>
       </c>
-      <c r="F61" s="70" t="s">
+      <c r="F61" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G61" s="71" t="s">
+      <c r="G61" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H61" s="46" t="s">
@@ -3060,16 +3271,16 @@
       <c r="C62" s="25">
         <v>46062</v>
       </c>
-      <c r="D62" s="73">
+      <c r="D62" s="22">
         <v>136524659</v>
       </c>
       <c r="E62" s="17">
         <v>3450238320</v>
       </c>
-      <c r="F62" s="70" t="s">
+      <c r="F62" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G62" s="71" t="s">
+      <c r="G62" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="46" t="s">
@@ -3089,16 +3300,16 @@
       <c r="C63" s="25">
         <v>46062</v>
       </c>
-      <c r="D63" s="73">
+      <c r="D63" s="22">
         <v>136502518</v>
       </c>
       <c r="E63" s="17">
         <v>3450237010</v>
       </c>
-      <c r="F63" s="70" t="s">
+      <c r="F63" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G63" s="71" t="s">
+      <c r="G63" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="46" t="s">
@@ -3118,16 +3329,16 @@
       <c r="C64" s="25">
         <v>46062</v>
       </c>
-      <c r="D64" s="73">
+      <c r="D64" s="22">
         <v>136512787</v>
       </c>
       <c r="E64" s="17">
         <v>3450237571</v>
       </c>
-      <c r="F64" s="70" t="s">
+      <c r="F64" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G64" s="71" t="s">
+      <c r="G64" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H64" s="46" t="s">
@@ -3147,16 +3358,16 @@
       <c r="C65" s="25">
         <v>46062</v>
       </c>
-      <c r="D65" s="73">
+      <c r="D65" s="22">
         <v>136509527</v>
       </c>
       <c r="E65" s="17">
         <v>3450237417</v>
       </c>
-      <c r="F65" s="70" t="s">
+      <c r="F65" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G65" s="71" t="s">
+      <c r="G65" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H65" s="46" t="s">
@@ -3176,16 +3387,16 @@
       <c r="C66" s="25">
         <v>46062</v>
       </c>
-      <c r="D66" s="73">
+      <c r="D66" s="22">
         <v>136521624</v>
       </c>
       <c r="E66" s="17">
         <v>3450238121</v>
       </c>
-      <c r="F66" s="70" t="s">
+      <c r="F66" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G66" s="71" t="s">
+      <c r="G66" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H66" s="46" t="s">
@@ -3205,16 +3416,16 @@
       <c r="C67" s="25">
         <v>46062</v>
       </c>
-      <c r="D67" s="73">
+      <c r="D67" s="22">
         <v>136528050</v>
       </c>
       <c r="E67" s="17">
         <v>3450238704</v>
       </c>
-      <c r="F67" s="70" t="s">
+      <c r="F67" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G67" s="71" t="s">
+      <c r="G67" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="46" t="s">
@@ -3234,16 +3445,16 @@
       <c r="C68" s="25">
         <v>46062</v>
       </c>
-      <c r="D68" s="73">
+      <c r="D68" s="22">
         <v>136534170</v>
       </c>
       <c r="E68" s="17">
         <v>3450239254</v>
       </c>
-      <c r="F68" s="70" t="s">
+      <c r="F68" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G68" s="71" t="s">
+      <c r="G68" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H68" s="46" t="s">
@@ -3263,16 +3474,16 @@
       <c r="C69" s="25">
         <v>46062</v>
       </c>
-      <c r="D69" s="73">
+      <c r="D69" s="22">
         <v>136528029</v>
       </c>
       <c r="E69" s="17">
         <v>3450238693</v>
       </c>
-      <c r="F69" s="70" t="s">
+      <c r="F69" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G69" s="71" t="s">
+      <c r="G69" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H69" s="46" t="s">
@@ -3292,16 +3503,16 @@
       <c r="C70" s="25">
         <v>46062</v>
       </c>
-      <c r="D70" s="73">
+      <c r="D70" s="22">
         <v>136525701</v>
       </c>
       <c r="E70" s="17">
         <v>3450238385</v>
       </c>
-      <c r="F70" s="70" t="s">
+      <c r="F70" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G70" s="71" t="s">
+      <c r="G70" s="67" t="s">
         <v>55</v>
       </c>
       <c r="H70" s="46" t="s">
@@ -3321,16 +3532,16 @@
       <c r="C71" s="25">
         <v>46062</v>
       </c>
-      <c r="D71" s="73">
+      <c r="D71" s="22">
         <v>136465176</v>
       </c>
       <c r="E71" s="17">
         <v>3450234205</v>
       </c>
-      <c r="F71" s="70" t="s">
+      <c r="F71" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G71" s="71" t="s">
+      <c r="G71" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H71" s="46" t="s">
@@ -3350,16 +3561,16 @@
       <c r="C72" s="25">
         <v>46062</v>
       </c>
-      <c r="D72" s="73">
+      <c r="D72" s="22">
         <v>136469438</v>
       </c>
       <c r="E72" s="17">
         <v>3450234436</v>
       </c>
-      <c r="F72" s="70" t="s">
+      <c r="F72" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G72" s="71" t="s">
+      <c r="G72" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="46" t="s">
@@ -3379,16 +3590,16 @@
       <c r="C73" s="25">
         <v>46062</v>
       </c>
-      <c r="D73" s="73">
+      <c r="D73" s="22">
         <v>136472331</v>
       </c>
       <c r="E73" s="17">
         <v>3450234623</v>
       </c>
-      <c r="F73" s="70" t="s">
+      <c r="F73" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G73" s="71" t="s">
+      <c r="G73" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H73" s="46" t="s">
@@ -3408,16 +3619,16 @@
       <c r="C74" s="25">
         <v>46062</v>
       </c>
-      <c r="D74" s="73">
+      <c r="D74" s="22">
         <v>136472778</v>
       </c>
       <c r="E74" s="17">
         <v>3450234656</v>
       </c>
-      <c r="F74" s="70" t="s">
+      <c r="F74" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G74" s="71" t="s">
+      <c r="G74" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H74" s="46" t="s">
@@ -3437,16 +3648,16 @@
       <c r="C75" s="25">
         <v>46062</v>
       </c>
-      <c r="D75" s="73">
+      <c r="D75" s="22">
         <v>136479528</v>
       </c>
       <c r="E75" s="17">
         <v>3450235030</v>
       </c>
-      <c r="F75" s="70" t="s">
+      <c r="F75" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G75" s="71" t="s">
+      <c r="G75" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H75" s="46" t="s">
@@ -3466,16 +3677,16 @@
       <c r="C76" s="25">
         <v>46062</v>
       </c>
-      <c r="D76" s="73">
+      <c r="D76" s="22">
         <v>136525845</v>
       </c>
       <c r="E76" s="17">
         <v>3450238407</v>
       </c>
-      <c r="F76" s="70" t="s">
+      <c r="F76" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G76" s="71" t="s">
+      <c r="G76" s="67" t="s">
         <v>33</v>
       </c>
       <c r="H76" s="46" t="s">
@@ -3495,16 +3706,16 @@
       <c r="C77" s="25">
         <v>46062</v>
       </c>
-      <c r="D77" s="73">
+      <c r="D77" s="22">
         <v>136482268</v>
       </c>
       <c r="E77" s="17">
         <v>3450233875</v>
       </c>
-      <c r="F77" s="70" t="s">
+      <c r="F77" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G77" s="71" t="s">
+      <c r="G77" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="46" t="s">
@@ -3524,16 +3735,16 @@
       <c r="C78" s="25">
         <v>46062</v>
       </c>
-      <c r="D78" s="73">
+      <c r="D78" s="22">
         <v>136482553</v>
       </c>
       <c r="E78" s="17">
         <v>3450235261</v>
       </c>
-      <c r="F78" s="70" t="s">
+      <c r="F78" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="71" t="s">
+      <c r="G78" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="46" t="s">
@@ -3553,16 +3764,16 @@
       <c r="C79" s="25">
         <v>46062</v>
       </c>
-      <c r="D79" s="73">
+      <c r="D79" s="22">
         <v>136483031</v>
       </c>
       <c r="E79" s="17">
         <v>3450234084</v>
       </c>
-      <c r="F79" s="70" t="s">
+      <c r="F79" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G79" s="71" t="s">
+      <c r="G79" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H79" s="46" t="s">
@@ -3582,16 +3793,16 @@
       <c r="C80" s="25">
         <v>46062</v>
       </c>
-      <c r="D80" s="73">
+      <c r="D80" s="22">
         <v>136484642</v>
       </c>
       <c r="E80" s="17">
         <v>3450235547</v>
       </c>
-      <c r="F80" s="70" t="s">
+      <c r="F80" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G80" s="71" t="s">
+      <c r="G80" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H80" s="46" t="s">
@@ -3611,16 +3822,16 @@
       <c r="C81" s="25">
         <v>46062</v>
       </c>
-      <c r="D81" s="73">
+      <c r="D81" s="22">
         <v>136484917</v>
       </c>
       <c r="E81" s="17">
         <v>3450235591</v>
       </c>
-      <c r="F81" s="70" t="s">
+      <c r="F81" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G81" s="71" t="s">
+      <c r="G81" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="46" t="s">
@@ -3640,16 +3851,16 @@
       <c r="C82" s="25">
         <v>46062</v>
       </c>
-      <c r="D82" s="73">
+      <c r="D82" s="22">
         <v>136485282</v>
       </c>
       <c r="E82" s="17">
         <v>3450235657</v>
       </c>
-      <c r="F82" s="70" t="s">
+      <c r="F82" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G82" s="71" t="s">
+      <c r="G82" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H82" s="46" t="s">
@@ -3669,16 +3880,16 @@
       <c r="C83" s="25">
         <v>46062</v>
       </c>
-      <c r="D83" s="73">
+      <c r="D83" s="22">
         <v>136485305</v>
       </c>
       <c r="E83" s="17">
         <v>3450235668</v>
       </c>
-      <c r="F83" s="70" t="s">
+      <c r="F83" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G83" s="71" t="s">
+      <c r="G83" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="46" t="s">
@@ -3698,16 +3909,16 @@
       <c r="C84" s="25">
         <v>46062</v>
       </c>
-      <c r="D84" s="73">
+      <c r="D84" s="22">
         <v>136487849</v>
       </c>
       <c r="E84" s="17">
         <v>3450235844</v>
       </c>
-      <c r="F84" s="70" t="s">
+      <c r="F84" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G84" s="71" t="s">
+      <c r="G84" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="46" t="s">
@@ -3727,16 +3938,16 @@
       <c r="C85" s="25">
         <v>46062</v>
       </c>
-      <c r="D85" s="73">
+      <c r="D85" s="22">
         <v>136487918</v>
       </c>
       <c r="E85" s="17">
         <v>3450235855</v>
       </c>
-      <c r="F85" s="70" t="s">
+      <c r="F85" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G85" s="71" t="s">
+      <c r="G85" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H85" s="46" t="s">
@@ -3756,16 +3967,16 @@
       <c r="C86" s="25">
         <v>46062</v>
       </c>
-      <c r="D86" s="73">
+      <c r="D86" s="22">
         <v>136488238</v>
       </c>
       <c r="E86" s="17">
         <v>3450235888</v>
       </c>
-      <c r="F86" s="70" t="s">
+      <c r="F86" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G86" s="71" t="s">
+      <c r="G86" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H86" s="46" t="s">
@@ -3785,16 +3996,16 @@
       <c r="C87" s="25">
         <v>46062</v>
       </c>
-      <c r="D87" s="73">
+      <c r="D87" s="22">
         <v>136490067</v>
       </c>
       <c r="E87" s="17">
         <v>3450236009</v>
       </c>
-      <c r="F87" s="70" t="s">
+      <c r="F87" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G87" s="71" t="s">
+      <c r="G87" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="46" t="s">
@@ -3814,16 +4025,16 @@
       <c r="C88" s="25">
         <v>46062</v>
       </c>
-      <c r="D88" s="73">
+      <c r="D88" s="22">
         <v>136490793</v>
       </c>
       <c r="E88" s="17">
         <v>3450236042</v>
       </c>
-      <c r="F88" s="70" t="s">
+      <c r="F88" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G88" s="71" t="s">
+      <c r="G88" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H88" s="46" t="s">
@@ -3843,16 +4054,16 @@
       <c r="C89" s="25">
         <v>46062</v>
       </c>
-      <c r="D89" s="73">
+      <c r="D89" s="22">
         <v>136491557</v>
       </c>
       <c r="E89" s="17">
         <v>3450236119</v>
       </c>
-      <c r="F89" s="70" t="s">
+      <c r="F89" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G89" s="71" t="s">
+      <c r="G89" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H89" s="46" t="s">
@@ -3872,16 +4083,16 @@
       <c r="C90" s="25">
         <v>46062</v>
       </c>
-      <c r="D90" s="73">
+      <c r="D90" s="22">
         <v>136492002</v>
       </c>
       <c r="E90" s="17">
         <v>3450236185</v>
       </c>
-      <c r="F90" s="70" t="s">
+      <c r="F90" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G90" s="71" t="s">
+      <c r="G90" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H90" s="46" t="s">
@@ -3901,16 +4112,16 @@
       <c r="C91" s="25">
         <v>46062</v>
       </c>
-      <c r="D91" s="73">
+      <c r="D91" s="22">
         <v>136493107</v>
       </c>
       <c r="E91" s="17">
         <v>3450236306</v>
       </c>
-      <c r="F91" s="70" t="s">
+      <c r="F91" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G91" s="71" t="s">
+      <c r="G91" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H91" s="46" t="s">
@@ -3930,16 +4141,16 @@
       <c r="C92" s="25">
         <v>46062</v>
       </c>
-      <c r="D92" s="73">
+      <c r="D92" s="22">
         <v>136493127</v>
       </c>
       <c r="E92" s="17">
         <v>3450236317</v>
       </c>
-      <c r="F92" s="70" t="s">
+      <c r="F92" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G92" s="71" t="s">
+      <c r="G92" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H92" s="46" t="s">
@@ -3959,16 +4170,16 @@
       <c r="C93" s="25">
         <v>46062</v>
       </c>
-      <c r="D93" s="73">
+      <c r="D93" s="22">
         <v>136493169</v>
       </c>
       <c r="E93" s="17">
         <v>3450236328</v>
       </c>
-      <c r="F93" s="70" t="s">
+      <c r="F93" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G93" s="71" t="s">
+      <c r="G93" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H93" s="45" t="s">
@@ -3988,16 +4199,16 @@
       <c r="C94" s="25">
         <v>46062</v>
       </c>
-      <c r="D94" s="73">
+      <c r="D94" s="22">
         <v>136493285</v>
       </c>
       <c r="E94" s="17">
         <v>3450236339</v>
       </c>
-      <c r="F94" s="70" t="s">
+      <c r="F94" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G94" s="71" t="s">
+      <c r="G94" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H94" s="45" t="s">
@@ -4017,16 +4228,16 @@
       <c r="C95" s="25">
         <v>46062</v>
       </c>
-      <c r="D95" s="73">
+      <c r="D95" s="22">
         <v>136493306</v>
       </c>
       <c r="E95" s="17">
         <v>3450236340</v>
       </c>
-      <c r="F95" s="70" t="s">
+      <c r="F95" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G95" s="71" t="s">
+      <c r="G95" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H95" s="45" t="s">
@@ -4046,16 +4257,16 @@
       <c r="C96" s="25">
         <v>46062</v>
       </c>
-      <c r="D96" s="73">
+      <c r="D96" s="22">
         <v>136493892</v>
       </c>
       <c r="E96" s="17">
         <v>3450236438</v>
       </c>
-      <c r="F96" s="70" t="s">
+      <c r="F96" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G96" s="71" t="s">
+      <c r="G96" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H96" s="45" t="s">
@@ -4075,16 +4286,16 @@
       <c r="C97" s="25">
         <v>46062</v>
       </c>
-      <c r="D97" s="73">
+      <c r="D97" s="22">
         <v>136494260</v>
       </c>
       <c r="E97" s="17">
         <v>3450236504</v>
       </c>
-      <c r="F97" s="70" t="s">
+      <c r="F97" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G97" s="71" t="s">
+      <c r="G97" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H97" s="45" t="s">
@@ -4104,16 +4315,16 @@
       <c r="C98" s="25">
         <v>46062</v>
       </c>
-      <c r="D98" s="73">
+      <c r="D98" s="22">
         <v>136494819</v>
       </c>
       <c r="E98" s="17">
         <v>3450236559</v>
       </c>
-      <c r="F98" s="70" t="s">
+      <c r="F98" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G98" s="71" t="s">
+      <c r="G98" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H98" s="45" t="s">
@@ -4133,16 +4344,16 @@
       <c r="C99" s="25">
         <v>46062</v>
       </c>
-      <c r="D99" s="73">
+      <c r="D99" s="22">
         <v>136495125</v>
       </c>
       <c r="E99" s="17">
         <v>3450236614</v>
       </c>
-      <c r="F99" s="70" t="s">
+      <c r="F99" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G99" s="71" t="s">
+      <c r="G99" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H99" s="45" t="s">
@@ -4162,16 +4373,16 @@
       <c r="C100" s="25">
         <v>46062</v>
       </c>
-      <c r="D100" s="73">
+      <c r="D100" s="22">
         <v>136496179</v>
       </c>
       <c r="E100" s="17">
         <v>3450236746</v>
       </c>
-      <c r="F100" s="70" t="s">
+      <c r="F100" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G100" s="71" t="s">
+      <c r="G100" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H100" s="45" t="s">
@@ -4182,43 +4393,59 @@
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B101" s="7">
+      <c r="A101" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="71">
         <v>46052</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="72">
         <v>46062</v>
       </c>
       <c r="D101" s="73">
         <v>136495243</v>
       </c>
-      <c r="E101" s="17">
+      <c r="E101" s="61">
         <v>3450236625</v>
       </c>
-      <c r="F101" s="70" t="s">
+      <c r="F101" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="G101" s="71" t="s">
+      <c r="G101" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="H101" s="45" t="s">
+      <c r="H101" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="I101" s="44">
+      <c r="I101" s="48">
         <v>46052</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="6"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="31"/>
-      <c r="G102" s="42"/>
-      <c r="H102" s="45"/>
+    <row r="102" spans="1:9" s="12" customFormat="1">
+      <c r="A102" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="44">
+        <v>46058</v>
+      </c>
+      <c r="C102" s="44">
+        <v>46062</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E102" s="68">
+        <v>3450242609</v>
+      </c>
+      <c r="F102" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="G102" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>133</v>
+      </c>
       <c r="I102" s="44"/>
     </row>
   </sheetData>
@@ -4241,17 +4468,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4265,19 +4492,19 @@
       <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="79" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="50" t="s">
@@ -4288,430 +4515,894 @@
       <c r="A2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="58"/>
+      <c r="B2" s="53">
+        <v>46051</v>
+      </c>
+      <c r="C2" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D2" s="80">
+        <v>136466416</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450234315</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="56">
+        <v>46051</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C3" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D3" s="80">
+        <v>136544694</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450239804</v>
+      </c>
+      <c r="F3" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="82" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C4" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D4" s="80">
+        <v>136546740</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450239969</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C5" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D5" s="80">
+        <v>136556983</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450241168</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C6" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D6" s="80">
+        <v>136549649</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450240387</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="83" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C7" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D7" s="80">
+        <v>136545020</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450239815</v>
+      </c>
+      <c r="F7" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C8" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D8" s="80">
+        <v>136550615</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450240519</v>
+      </c>
+      <c r="F8" s="76" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C9" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D9" s="80">
+        <v>136554112</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450240882</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C10" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D10" s="80">
+        <v>136547307</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450240013</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="7">
+        <v>46060</v>
+      </c>
+      <c r="C11" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D11" s="80">
+        <v>136577555</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450242940</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46059</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C12" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D12" s="80">
+        <v>136574106</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450242532</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46063</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C13" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D13" s="80">
+        <v>136569897</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450241718</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46058</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C14" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D14" s="80">
+        <v>136590604</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450243478</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C15" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D15" s="80">
+        <v>136605541</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450244699</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46059</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C16" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D16" s="80">
+        <v>136589134</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450243379</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46059</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C17" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D17" s="80">
+        <v>136551257</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450240585</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>155</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46049</v>
+      </c>
+      <c r="C18" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D18" s="80">
+        <v>136432160</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450231510</v>
+      </c>
+      <c r="F18" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46051</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C19" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D19" s="80">
+        <v>136556297</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450241080</v>
+      </c>
+      <c r="F19" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C20" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D20" s="80">
+        <v>136548776</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450240244</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="82" t="s">
+        <v>161</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C21" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D21" s="80">
+        <v>136463403</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450233897</v>
+      </c>
+      <c r="F21" s="76" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" s="44">
+        <v>46059</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C22" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D22" s="80">
+        <v>136549076</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450240288</v>
+      </c>
+      <c r="F22" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="82" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46057</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
+      <c r="B23" s="7">
+        <v>46056</v>
+      </c>
+      <c r="C23" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D23" s="80">
+        <v>136526134</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450238451</v>
+      </c>
+      <c r="F23" s="76" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="82" t="s">
+        <v>167</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46056</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
+      <c r="B24" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C24" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D24" s="80">
+        <v>136513461</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450237615</v>
+      </c>
+      <c r="F24" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="82" t="s">
+        <v>169</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46055</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
+      <c r="B25" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C25" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D25" s="80">
+        <v>136580070</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450243170</v>
+      </c>
+      <c r="F25" s="76" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
+      <c r="B26" s="7">
+        <v>46056</v>
+      </c>
+      <c r="C26" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D26" s="80">
+        <v>136524183</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450238275</v>
+      </c>
+      <c r="F26" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="82" t="s">
+        <v>172</v>
+      </c>
+      <c r="I26" s="44">
+        <v>46056</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
+      <c r="B27" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C27" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D27" s="80">
+        <v>136500753</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450236966</v>
+      </c>
+      <c r="F27" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
+      <c r="B28" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C28" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D28" s="80">
+        <v>136512866</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450237582</v>
+      </c>
+      <c r="F28" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="44">
+        <v>46062</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C29" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D29" s="80">
+        <v>136498050</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450236834</v>
+      </c>
+      <c r="F29" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="44">
+        <v>46053</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="B30" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C30" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D30" s="80">
+        <v>136499606</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450236284</v>
+      </c>
+      <c r="F30" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="44">
+        <v>46052</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="B31" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C31" s="54">
+        <v>46063</v>
+      </c>
+      <c r="D31" s="80">
+        <v>136499685</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450235734</v>
+      </c>
+      <c r="F31" s="76" t="s">
+        <v>177</v>
+      </c>
+      <c r="G31" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="48">
+        <v>46052</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="58"/>
       <c r="I32" s="44"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G32" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4767,20 +5458,20 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="57"/>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="57"/>
       <c r="C3" s="25"/>
       <c r="D3" s="26"/>
       <c r="E3" s="17"/>
@@ -4808,18 +5499,18 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="64"/>
       <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="25"/>
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
@@ -4832,7 +5523,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="25"/>
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
@@ -4845,7 +5536,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="25"/>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -4858,7 +5549,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="25"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
@@ -4871,12 +5562,12 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="25"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="62"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="12"/>
       <c r="I10" s="44"/>
     </row>
@@ -4884,7 +5575,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="57"/>
       <c r="C11" s="25"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
@@ -4897,12 +5588,12 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="25"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="62"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="12"/>
       <c r="I12" s="44"/>
     </row>
@@ -4910,7 +5601,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="57"/>
       <c r="C13" s="25"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
@@ -4923,7 +5614,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="25"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
@@ -4936,12 +5627,12 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="25"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="12"/>
       <c r="I15" s="44"/>
     </row>
@@ -4949,7 +5640,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="25"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
@@ -4962,7 +5653,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="60"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="25"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
@@ -5019,7 +5710,7 @@
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="62"/>
+      <c r="G21" s="59"/>
       <c r="H21" s="12"/>
       <c r="I21" s="44"/>
     </row>
@@ -5040,10 +5731,10 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="56"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="69"/>
+      <c r="G23" s="66"/>
       <c r="H23" s="14"/>
     </row>
     <row r="24" spans="1:9">

--- a/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96801450-6965-400D-B623-6761E905D9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{158B6020-25E3-47B3-841D-EC546666E6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="09.02" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="211">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -594,6 +594,111 @@
   </si>
   <si>
     <t xml:space="preserve">EMANUELLA CERVEIRA DE ANDRADE CUNHA          </t>
+  </si>
+  <si>
+    <t>ELISON DE LIMA ANDRADE CPF 5681797490</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 10.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE MAGNO CAPORAL CUNHA                </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE bonificação está incorreta, apólice anterior consta cla
+sse de bônus 1, não havendo sinistro, conforme regra concede 1 cla
+sse debônus, assim sendo o correto bônus 2, não 3 como foi transmi
+tido.
+Com a correção ficou 10x R$ 332,89. Podemos emitir desta
+forma?</t>
+  </si>
+  <si>
+    <t>I A S SERVICOS TRANSPORTES E COMERCIO LTDA EP</t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: HODÕMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIVALDO NASCIMENTO ALVES                    </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTOS: Documento da moto, Painel com a motocicleta ligada, Número do Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA REGINA LOPES DA SILVA CAVALCANTE      </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi Justificativa de Dados Divergentes: Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO DANIEL CARRIS RIEDIGER              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGAMENON GOMES MARTINS FILHO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA PAIXAO DO NASCIMENTO                 </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO EXPIRADO FOTOS: Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro, Frente e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIENE RODRIGUES DE SOUSA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ALDO JESUS SANTOS                       </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do motorista, Frente e lateral do passageiro, Traseira e lateral do motorista (Foto não enquadrada corretamente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENTIM TERRA VIVA ALIMENTOS LTDA ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS // CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAIDE ALBERTA VALERIANO DA COSTA            </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 10.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLINIO FLORES                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro e motorista, Traseira e lateral do passageiro e motorista, Motor, Chassi. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCILENE APARECIDA MANGINI FRARE            </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro e motorista, Motor, Porta malas aberto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILMARA FERNANDES RODRIGUES SANTOS           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA FRANCISCO DE MELO ARAUJO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO MACHADO TEDESCO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA CABRAL FERREIRA MENEGUSSI            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA ROSSELLI ALENCAR BOERI            </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi, Frente e lateral do motorista, Frente e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S R DA SILVA PECAS E SERVICOS DE MOTOS ME    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO JULIO MANSANO NETO                 </t>
   </si>
 </sst>
 </file>
@@ -664,7 +769,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -840,17 +945,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -859,17 +953,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -923,7 +1006,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -975,14 +1058,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1063,9 +1140,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1076,24 +1150,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1108,18 +1169,17 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1127,9 +1187,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1143,6 +1200,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1528,10 +1590,10 @@
       <c r="B2" s="7">
         <v>46051</v>
       </c>
-      <c r="C2" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D2" s="22">
+      <c r="C2" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D2" s="21">
         <v>136458414</v>
       </c>
       <c r="E2" s="17">
@@ -1540,13 +1602,13 @@
       <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1557,10 +1619,10 @@
       <c r="B3" s="7">
         <v>46050</v>
       </c>
-      <c r="C3" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D3" s="22">
+      <c r="C3" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D3" s="21">
         <v>136465260</v>
       </c>
       <c r="E3" s="17">
@@ -1569,13 +1631,13 @@
       <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -1586,10 +1648,10 @@
       <c r="B4" s="7">
         <v>46051</v>
       </c>
-      <c r="C4" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D4" s="22">
+      <c r="C4" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D4" s="21">
         <v>136471203</v>
       </c>
       <c r="E4" s="17">
@@ -1598,13 +1660,13 @@
       <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1615,10 +1677,10 @@
       <c r="B5" s="7">
         <v>46051</v>
       </c>
-      <c r="C5" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D5" s="22">
+      <c r="C5" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D5" s="21">
         <v>136473444</v>
       </c>
       <c r="E5" s="17">
@@ -1627,13 +1689,13 @@
       <c r="F5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1644,10 +1706,10 @@
       <c r="B6" s="7">
         <v>46051</v>
       </c>
-      <c r="C6" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D6" s="22">
+      <c r="C6" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D6" s="21">
         <v>136458429</v>
       </c>
       <c r="E6" s="17">
@@ -1656,13 +1718,13 @@
       <c r="F6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1673,10 +1735,10 @@
       <c r="B7" s="7">
         <v>46051</v>
       </c>
-      <c r="C7" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D7" s="21">
         <v>136461389</v>
       </c>
       <c r="E7" s="17">
@@ -1685,13 +1747,13 @@
       <c r="F7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1702,10 +1764,10 @@
       <c r="B8" s="7">
         <v>46051</v>
       </c>
-      <c r="C8" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D8" s="22">
+      <c r="C8" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D8" s="21">
         <v>136474453</v>
       </c>
       <c r="E8" s="17">
@@ -1714,13 +1776,13 @@
       <c r="F8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1731,10 +1793,10 @@
       <c r="B9" s="7">
         <v>46051</v>
       </c>
-      <c r="C9" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D9" s="22">
+      <c r="C9" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D9" s="21">
         <v>136475756</v>
       </c>
       <c r="E9" s="17">
@@ -1743,13 +1805,13 @@
       <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="67" t="s">
+      <c r="G9" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1760,10 +1822,10 @@
       <c r="B10" s="7">
         <v>46051</v>
       </c>
-      <c r="C10" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D10" s="22">
+      <c r="C10" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D10" s="21">
         <v>136472176</v>
       </c>
       <c r="E10" s="17">
@@ -1772,13 +1834,13 @@
       <c r="F10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -1789,10 +1851,10 @@
       <c r="B11" s="7">
         <v>46052</v>
       </c>
-      <c r="C11" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D11" s="22">
+      <c r="C11" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D11" s="21">
         <v>136482435</v>
       </c>
       <c r="E11" s="17">
@@ -1801,13 +1863,13 @@
       <c r="F11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="67" t="s">
+      <c r="G11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1818,10 +1880,10 @@
       <c r="B12" s="7">
         <v>46052</v>
       </c>
-      <c r="C12" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D12" s="22">
+      <c r="C12" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D12" s="21">
         <v>136482788</v>
       </c>
       <c r="E12" s="17">
@@ -1830,13 +1892,13 @@
       <c r="F12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1847,10 +1909,10 @@
       <c r="B13" s="7">
         <v>46052</v>
       </c>
-      <c r="C13" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D13" s="22">
+      <c r="C13" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D13" s="21">
         <v>136492609</v>
       </c>
       <c r="E13" s="17">
@@ -1859,13 +1921,13 @@
       <c r="F13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="67" t="s">
+      <c r="G13" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1876,10 +1938,10 @@
       <c r="B14" s="7">
         <v>46052</v>
       </c>
-      <c r="C14" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D14" s="22">
+      <c r="C14" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D14" s="21">
         <v>136493802</v>
       </c>
       <c r="E14" s="17">
@@ -1888,13 +1950,13 @@
       <c r="F14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1905,10 +1967,10 @@
       <c r="B15" s="7">
         <v>46052</v>
       </c>
-      <c r="C15" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D15" s="22">
+      <c r="C15" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D15" s="21">
         <v>136492072</v>
       </c>
       <c r="E15" s="17">
@@ -1917,13 +1979,13 @@
       <c r="F15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G15" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1934,10 +1996,10 @@
       <c r="B16" s="7">
         <v>46052</v>
       </c>
-      <c r="C16" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="C16" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D16" s="21">
         <v>136493898</v>
       </c>
       <c r="E16" s="17">
@@ -1946,13 +2008,13 @@
       <c r="F16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="67" t="s">
+      <c r="G16" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1963,10 +2025,10 @@
       <c r="B17" s="7">
         <v>46052</v>
       </c>
-      <c r="C17" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D17" s="22">
+      <c r="C17" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D17" s="21">
         <v>136495966</v>
       </c>
       <c r="E17" s="17">
@@ -1975,13 +2037,13 @@
       <c r="F17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -1992,10 +2054,10 @@
       <c r="B18" s="7">
         <v>46052</v>
       </c>
-      <c r="C18" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D18" s="22">
+      <c r="C18" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D18" s="21">
         <v>136494395</v>
       </c>
       <c r="E18" s="17">
@@ -2004,13 +2066,13 @@
       <c r="F18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="67" t="s">
+      <c r="G18" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2021,10 +2083,10 @@
       <c r="B19" s="7">
         <v>46052</v>
       </c>
-      <c r="C19" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D19" s="22">
+      <c r="C19" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D19" s="21">
         <v>136497331</v>
       </c>
       <c r="E19" s="17">
@@ -2033,13 +2095,13 @@
       <c r="F19" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="67" t="s">
+      <c r="G19" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2050,10 +2112,10 @@
       <c r="B20" s="7">
         <v>46052</v>
       </c>
-      <c r="C20" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D20" s="22">
+      <c r="C20" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D20" s="21">
         <v>136496525</v>
       </c>
       <c r="E20" s="17">
@@ -2062,13 +2124,13 @@
       <c r="F20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="67" t="s">
+      <c r="G20" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2079,10 +2141,10 @@
       <c r="B21" s="7">
         <v>46052</v>
       </c>
-      <c r="C21" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D21" s="22">
+      <c r="C21" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D21" s="21">
         <v>136478940</v>
       </c>
       <c r="E21" s="17">
@@ -2091,13 +2153,13 @@
       <c r="F21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="G21" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2108,10 +2170,10 @@
       <c r="B22" s="7">
         <v>46052</v>
       </c>
-      <c r="C22" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D22" s="22">
+      <c r="C22" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D22" s="21">
         <v>136484224</v>
       </c>
       <c r="E22" s="17">
@@ -2120,13 +2182,13 @@
       <c r="F22" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="G22" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2137,10 +2199,10 @@
       <c r="B23" s="7">
         <v>46052</v>
       </c>
-      <c r="C23" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D23" s="22">
+      <c r="C23" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D23" s="21">
         <v>136495664</v>
       </c>
       <c r="E23" s="17">
@@ -2149,13 +2211,13 @@
       <c r="F23" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2166,10 +2228,10 @@
       <c r="B24" s="7">
         <v>46055</v>
       </c>
-      <c r="C24" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D24" s="22">
+      <c r="C24" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D24" s="21">
         <v>136517042</v>
       </c>
       <c r="E24" s="17">
@@ -2178,13 +2240,13 @@
       <c r="F24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -2195,10 +2257,10 @@
       <c r="B25" s="7">
         <v>46055</v>
       </c>
-      <c r="C25" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D25" s="22">
+      <c r="C25" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D25" s="21">
         <v>136507603</v>
       </c>
       <c r="E25" s="17">
@@ -2207,13 +2269,13 @@
       <c r="F25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -2224,10 +2286,10 @@
       <c r="B26" s="7">
         <v>46056</v>
       </c>
-      <c r="C26" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D26" s="22">
+      <c r="C26" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D26" s="21">
         <v>136529840</v>
       </c>
       <c r="E26" s="17">
@@ -2236,13 +2298,13 @@
       <c r="F26" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2253,10 +2315,10 @@
       <c r="B27" s="7">
         <v>46056</v>
       </c>
-      <c r="C27" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D27" s="22">
+      <c r="C27" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D27" s="21">
         <v>136532121</v>
       </c>
       <c r="E27" s="17">
@@ -2265,13 +2327,13 @@
       <c r="F27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="G27" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -2282,10 +2344,10 @@
       <c r="B28" s="7">
         <v>46056</v>
       </c>
-      <c r="C28" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D28" s="22">
+      <c r="C28" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D28" s="21">
         <v>136530866</v>
       </c>
       <c r="E28" s="17">
@@ -2294,13 +2356,13 @@
       <c r="F28" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="67" t="s">
+      <c r="G28" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2311,10 +2373,10 @@
       <c r="B29" s="7">
         <v>46056</v>
       </c>
-      <c r="C29" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D29" s="22">
+      <c r="C29" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D29" s="21">
         <v>136537723</v>
       </c>
       <c r="E29" s="17">
@@ -2323,13 +2385,13 @@
       <c r="F29" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="67" t="s">
+      <c r="G29" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2340,10 +2402,10 @@
       <c r="B30" s="7">
         <v>46056</v>
       </c>
-      <c r="C30" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D30" s="22">
+      <c r="C30" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D30" s="21">
         <v>136530551</v>
       </c>
       <c r="E30" s="17">
@@ -2352,13 +2414,13 @@
       <c r="F30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="67" t="s">
+      <c r="G30" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="45" t="s">
+      <c r="H30" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2369,10 +2431,10 @@
       <c r="B31" s="7">
         <v>46056</v>
       </c>
-      <c r="C31" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D31" s="22">
+      <c r="C31" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D31" s="21">
         <v>136532327</v>
       </c>
       <c r="E31" s="17">
@@ -2381,13 +2443,13 @@
       <c r="F31" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="67" t="s">
+      <c r="G31" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2398,10 +2460,10 @@
       <c r="B32" s="7">
         <v>46051</v>
       </c>
-      <c r="C32" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D32" s="22">
+      <c r="C32" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D32" s="21">
         <v>136473711</v>
       </c>
       <c r="E32" s="17">
@@ -2410,13 +2472,13 @@
       <c r="F32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="67" t="s">
+      <c r="G32" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -2427,10 +2489,10 @@
       <c r="B33" s="7">
         <v>46056</v>
       </c>
-      <c r="C33" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D33" s="22">
+      <c r="C33" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D33" s="21">
         <v>136528085</v>
       </c>
       <c r="E33" s="17">
@@ -2439,13 +2501,13 @@
       <c r="F33" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G33" s="67" t="s">
+      <c r="G33" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2456,10 +2518,10 @@
       <c r="B34" s="7">
         <v>46052</v>
       </c>
-      <c r="C34" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D34" s="22">
+      <c r="C34" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D34" s="21">
         <v>136483835</v>
       </c>
       <c r="E34" s="17">
@@ -2468,13 +2530,13 @@
       <c r="F34" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="67" t="s">
+      <c r="G34" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -2485,10 +2547,10 @@
       <c r="B35" s="7">
         <v>46052</v>
       </c>
-      <c r="C35" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D35" s="22">
+      <c r="C35" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D35" s="21">
         <v>136485047</v>
       </c>
       <c r="E35" s="17">
@@ -2497,13 +2559,13 @@
       <c r="F35" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="67" t="s">
+      <c r="G35" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2514,10 +2576,10 @@
       <c r="B36" s="7">
         <v>46058</v>
       </c>
-      <c r="C36" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D36" s="22">
+      <c r="C36" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D36" s="21">
         <v>136570165</v>
       </c>
       <c r="E36" s="17">
@@ -2526,13 +2588,13 @@
       <c r="F36" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G36" s="67" t="s">
+      <c r="G36" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="42">
         <v>46058</v>
       </c>
     </row>
@@ -2543,10 +2605,10 @@
       <c r="B37" s="7">
         <v>46058</v>
       </c>
-      <c r="C37" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D37" s="22">
+      <c r="C37" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D37" s="21">
         <v>136576941</v>
       </c>
       <c r="E37" s="17">
@@ -2555,13 +2617,13 @@
       <c r="F37" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="67" t="s">
+      <c r="G37" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="42">
         <v>46058</v>
       </c>
     </row>
@@ -2572,10 +2634,10 @@
       <c r="B38" s="7">
         <v>46056</v>
       </c>
-      <c r="C38" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D38" s="22">
+      <c r="C38" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D38" s="21">
         <v>136522475</v>
       </c>
       <c r="E38" s="17">
@@ -2584,13 +2646,13 @@
       <c r="F38" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="67" t="s">
+      <c r="G38" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -2601,10 +2663,10 @@
       <c r="B39" s="7">
         <v>46059</v>
       </c>
-      <c r="C39" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D39" s="22">
+      <c r="C39" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D39" s="21">
         <v>136572095</v>
       </c>
       <c r="E39" s="17">
@@ -2613,13 +2675,13 @@
       <c r="F39" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="67" t="s">
+      <c r="G39" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H39" s="46" t="s">
+      <c r="H39" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -2630,10 +2692,10 @@
       <c r="B40" s="7">
         <v>46052</v>
       </c>
-      <c r="C40" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D40" s="22">
+      <c r="C40" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D40" s="21">
         <v>136496014</v>
       </c>
       <c r="E40" s="17">
@@ -2642,13 +2704,13 @@
       <c r="F40" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="67" t="s">
+      <c r="G40" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="46" t="s">
+      <c r="H40" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2659,10 +2721,10 @@
       <c r="B41" s="7">
         <v>46055</v>
       </c>
-      <c r="C41" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D41" s="22">
+      <c r="C41" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D41" s="21">
         <v>136510993</v>
       </c>
       <c r="E41" s="17">
@@ -2671,13 +2733,13 @@
       <c r="F41" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G41" s="67" t="s">
+      <c r="G41" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="46" t="s">
+      <c r="H41" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -2688,10 +2750,10 @@
       <c r="B42" s="7">
         <v>46050</v>
       </c>
-      <c r="C42" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D42" s="22">
+      <c r="C42" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D42" s="21">
         <v>136445487</v>
       </c>
       <c r="E42" s="17">
@@ -2700,13 +2762,13 @@
       <c r="F42" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="67" t="s">
+      <c r="G42" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="46" t="s">
+      <c r="H42" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2717,10 +2779,10 @@
       <c r="B43" s="7">
         <v>46050</v>
       </c>
-      <c r="C43" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D43" s="22">
+      <c r="C43" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D43" s="21">
         <v>136448051</v>
       </c>
       <c r="E43" s="17">
@@ -2729,13 +2791,13 @@
       <c r="F43" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G43" s="67" t="s">
+      <c r="G43" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="46" t="s">
+      <c r="H43" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2746,10 +2808,10 @@
       <c r="B44" s="7">
         <v>46049</v>
       </c>
-      <c r="C44" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D44" s="22">
+      <c r="C44" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D44" s="21">
         <v>136440998</v>
       </c>
       <c r="E44" s="17">
@@ -2758,13 +2820,13 @@
       <c r="F44" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="67" t="s">
+      <c r="G44" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="46" t="s">
+      <c r="H44" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="42">
         <v>46049</v>
       </c>
     </row>
@@ -2775,10 +2837,10 @@
       <c r="B45" s="7">
         <v>46050</v>
       </c>
-      <c r="C45" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D45" s="22">
+      <c r="C45" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D45" s="21">
         <v>136448132</v>
       </c>
       <c r="E45" s="17">
@@ -2787,13 +2849,13 @@
       <c r="F45" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G45" s="67" t="s">
+      <c r="G45" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="46" t="s">
+      <c r="H45" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2804,10 +2866,10 @@
       <c r="B46" s="7">
         <v>46050</v>
       </c>
-      <c r="C46" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D46" s="22">
+      <c r="C46" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D46" s="21">
         <v>136448415</v>
       </c>
       <c r="E46" s="17">
@@ -2816,13 +2878,13 @@
       <c r="F46" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="67" t="s">
+      <c r="G46" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="46" t="s">
+      <c r="H46" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2833,10 +2895,10 @@
       <c r="B47" s="7">
         <v>46050</v>
       </c>
-      <c r="C47" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D47" s="22">
+      <c r="C47" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D47" s="21">
         <v>136453329</v>
       </c>
       <c r="E47" s="17">
@@ -2845,13 +2907,13 @@
       <c r="F47" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="67" t="s">
+      <c r="G47" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="46" t="s">
+      <c r="H47" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -2862,10 +2924,10 @@
       <c r="B48" s="7">
         <v>46050</v>
       </c>
-      <c r="C48" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D48" s="22">
+      <c r="C48" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D48" s="21">
         <v>136446494</v>
       </c>
       <c r="E48" s="17">
@@ -2874,13 +2936,13 @@
       <c r="F48" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G48" s="67" t="s">
+      <c r="G48" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="46" t="s">
+      <c r="H48" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2891,10 +2953,10 @@
       <c r="B49" s="7">
         <v>46050</v>
       </c>
-      <c r="C49" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D49" s="22">
+      <c r="C49" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D49" s="21">
         <v>136448763</v>
       </c>
       <c r="E49" s="17">
@@ -2903,13 +2965,13 @@
       <c r="F49" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G49" s="67" t="s">
+      <c r="G49" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="46" t="s">
+      <c r="H49" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2920,10 +2982,10 @@
       <c r="B50" s="7">
         <v>46050</v>
       </c>
-      <c r="C50" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D50" s="22">
+      <c r="C50" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D50" s="21">
         <v>136443035</v>
       </c>
       <c r="E50" s="17">
@@ -2932,13 +2994,13 @@
       <c r="F50" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G50" s="67" t="s">
+      <c r="G50" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="46" t="s">
+      <c r="H50" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2949,10 +3011,10 @@
       <c r="B51" s="7">
         <v>46050</v>
       </c>
-      <c r="C51" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D51" s="22">
+      <c r="C51" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D51" s="21">
         <v>136449209</v>
       </c>
       <c r="E51" s="17">
@@ -2961,13 +3023,13 @@
       <c r="F51" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G51" s="67" t="s">
+      <c r="G51" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="46" t="s">
+      <c r="H51" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -2978,10 +3040,10 @@
       <c r="B52" s="7">
         <v>46050</v>
       </c>
-      <c r="C52" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D52" s="22">
+      <c r="C52" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D52" s="21">
         <v>136450518</v>
       </c>
       <c r="E52" s="17">
@@ -2990,13 +3052,13 @@
       <c r="F52" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G52" s="67" t="s">
+      <c r="G52" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H52" s="46" t="s">
+      <c r="H52" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3007,10 +3069,10 @@
       <c r="B53" s="7">
         <v>46071</v>
       </c>
-      <c r="C53" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D53" s="22">
+      <c r="C53" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D53" s="21">
         <v>136451363</v>
       </c>
       <c r="E53" s="17">
@@ -3019,13 +3081,13 @@
       <c r="F53" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G53" s="67" t="s">
+      <c r="G53" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H53" s="46" t="s">
+      <c r="H53" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3036,10 +3098,10 @@
       <c r="B54" s="7">
         <v>46050</v>
       </c>
-      <c r="C54" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D54" s="22">
+      <c r="C54" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D54" s="21">
         <v>136451835</v>
       </c>
       <c r="E54" s="17">
@@ -3048,13 +3110,13 @@
       <c r="F54" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G54" s="67" t="s">
+      <c r="G54" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="46" t="s">
+      <c r="H54" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3065,10 +3127,10 @@
       <c r="B55" s="7">
         <v>46049</v>
       </c>
-      <c r="C55" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D55" s="22">
+      <c r="C55" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D55" s="21">
         <v>136439942</v>
       </c>
       <c r="E55" s="17">
@@ -3077,13 +3139,13 @@
       <c r="F55" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G55" s="67" t="s">
+      <c r="G55" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H55" s="46" t="s">
+      <c r="H55" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="42">
         <v>46049</v>
       </c>
     </row>
@@ -3094,10 +3156,10 @@
       <c r="B56" s="7">
         <v>46050</v>
       </c>
-      <c r="C56" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D56" s="22">
+      <c r="C56" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D56" s="21">
         <v>136448511</v>
       </c>
       <c r="E56" s="17">
@@ -3106,13 +3168,13 @@
       <c r="F56" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G56" s="67" t="s">
+      <c r="G56" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="46" t="s">
+      <c r="H56" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3123,10 +3185,10 @@
       <c r="B57" s="7">
         <v>46049</v>
       </c>
-      <c r="C57" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D57" s="22">
+      <c r="C57" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D57" s="21">
         <v>136440268</v>
       </c>
       <c r="E57" s="17">
@@ -3135,13 +3197,13 @@
       <c r="F57" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G57" s="67" t="s">
+      <c r="G57" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H57" s="46" t="s">
+      <c r="H57" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="42">
         <v>46049</v>
       </c>
     </row>
@@ -3152,10 +3214,10 @@
       <c r="B58" s="7">
         <v>46050</v>
       </c>
-      <c r="C58" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D58" s="22">
+      <c r="C58" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D58" s="21">
         <v>136454528</v>
       </c>
       <c r="E58" s="17">
@@ -3164,13 +3226,13 @@
       <c r="F58" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G58" s="67" t="s">
+      <c r="G58" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="46" t="s">
+      <c r="H58" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3181,10 +3243,10 @@
       <c r="B59" s="7">
         <v>46049</v>
       </c>
-      <c r="C59" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D59" s="22">
+      <c r="C59" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D59" s="21">
         <v>136438866</v>
       </c>
       <c r="E59" s="17">
@@ -3193,13 +3255,13 @@
       <c r="F59" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G59" s="67" t="s">
+      <c r="G59" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="46" t="s">
+      <c r="H59" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="42">
         <v>46049</v>
       </c>
     </row>
@@ -3210,10 +3272,10 @@
       <c r="B60" s="7">
         <v>46050</v>
       </c>
-      <c r="C60" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D60" s="22">
+      <c r="C60" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D60" s="21">
         <v>136446064</v>
       </c>
       <c r="E60" s="17">
@@ -3222,13 +3284,13 @@
       <c r="F60" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G60" s="67" t="s">
+      <c r="G60" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="46" t="s">
+      <c r="H60" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3239,10 +3301,10 @@
       <c r="B61" s="7">
         <v>46050</v>
       </c>
-      <c r="C61" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D61" s="22">
+      <c r="C61" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D61" s="21">
         <v>136446666</v>
       </c>
       <c r="E61" s="17">
@@ -3251,13 +3313,13 @@
       <c r="F61" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G61" s="67" t="s">
+      <c r="G61" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="46" t="s">
+      <c r="H61" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="42">
         <v>46050</v>
       </c>
     </row>
@@ -3268,10 +3330,10 @@
       <c r="B62" s="7">
         <v>46056</v>
       </c>
-      <c r="C62" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D62" s="22">
+      <c r="C62" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D62" s="21">
         <v>136524659</v>
       </c>
       <c r="E62" s="17">
@@ -3280,13 +3342,13 @@
       <c r="F62" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G62" s="67" t="s">
+      <c r="G62" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H62" s="46" t="s">
+      <c r="H62" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3297,10 +3359,10 @@
       <c r="B63" s="7">
         <v>46055</v>
       </c>
-      <c r="C63" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D63" s="22">
+      <c r="C63" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D63" s="21">
         <v>136502518</v>
       </c>
       <c r="E63" s="17">
@@ -3309,13 +3371,13 @@
       <c r="F63" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G63" s="67" t="s">
+      <c r="G63" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H63" s="46" t="s">
+      <c r="H63" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -3326,10 +3388,10 @@
       <c r="B64" s="7">
         <v>46055</v>
       </c>
-      <c r="C64" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D64" s="22">
+      <c r="C64" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D64" s="21">
         <v>136512787</v>
       </c>
       <c r="E64" s="17">
@@ -3338,13 +3400,13 @@
       <c r="F64" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G64" s="67" t="s">
+      <c r="G64" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H64" s="46" t="s">
+      <c r="H64" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -3355,10 +3417,10 @@
       <c r="B65" s="7">
         <v>46063</v>
       </c>
-      <c r="C65" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D65" s="22">
+      <c r="C65" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D65" s="21">
         <v>136509527</v>
       </c>
       <c r="E65" s="17">
@@ -3367,13 +3429,13 @@
       <c r="F65" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G65" s="67" t="s">
+      <c r="G65" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H65" s="46" t="s">
+      <c r="H65" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="I65" s="44">
+      <c r="I65" s="42">
         <v>46063</v>
       </c>
     </row>
@@ -3384,10 +3446,10 @@
       <c r="B66" s="7">
         <v>46056</v>
       </c>
-      <c r="C66" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D66" s="22">
+      <c r="C66" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D66" s="21">
         <v>136521624</v>
       </c>
       <c r="E66" s="17">
@@ -3396,13 +3458,13 @@
       <c r="F66" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G66" s="67" t="s">
+      <c r="G66" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H66" s="46" t="s">
+      <c r="H66" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I66" s="44">
+      <c r="I66" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3413,10 +3475,10 @@
       <c r="B67" s="7">
         <v>46056</v>
       </c>
-      <c r="C67" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D67" s="22">
+      <c r="C67" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D67" s="21">
         <v>136528050</v>
       </c>
       <c r="E67" s="17">
@@ -3425,13 +3487,13 @@
       <c r="F67" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G67" s="67" t="s">
+      <c r="G67" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H67" s="46" t="s">
+      <c r="H67" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I67" s="44">
+      <c r="I67" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3442,10 +3504,10 @@
       <c r="B68" s="7">
         <v>46056</v>
       </c>
-      <c r="C68" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D68" s="22">
+      <c r="C68" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D68" s="21">
         <v>136534170</v>
       </c>
       <c r="E68" s="17">
@@ -3454,13 +3516,13 @@
       <c r="F68" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G68" s="67" t="s">
+      <c r="G68" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H68" s="46" t="s">
+      <c r="H68" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I68" s="44">
+      <c r="I68" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3471,10 +3533,10 @@
       <c r="B69" s="7">
         <v>46056</v>
       </c>
-      <c r="C69" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D69" s="22">
+      <c r="C69" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D69" s="21">
         <v>136528029</v>
       </c>
       <c r="E69" s="17">
@@ -3483,13 +3545,13 @@
       <c r="F69" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G69" s="67" t="s">
+      <c r="G69" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="46" t="s">
+      <c r="H69" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I69" s="44">
+      <c r="I69" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3500,10 +3562,10 @@
       <c r="B70" s="7">
         <v>46056</v>
       </c>
-      <c r="C70" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D70" s="22">
+      <c r="C70" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D70" s="21">
         <v>136525701</v>
       </c>
       <c r="E70" s="17">
@@ -3512,13 +3574,13 @@
       <c r="F70" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G70" s="67" t="s">
+      <c r="G70" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H70" s="46" t="s">
+      <c r="H70" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I70" s="44">
+      <c r="I70" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3529,10 +3591,10 @@
       <c r="B71" s="7">
         <v>46051</v>
       </c>
-      <c r="C71" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D71" s="22">
+      <c r="C71" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D71" s="21">
         <v>136465176</v>
       </c>
       <c r="E71" s="17">
@@ -3541,13 +3603,13 @@
       <c r="F71" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G71" s="67" t="s">
+      <c r="G71" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="46" t="s">
+      <c r="H71" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I71" s="44">
+      <c r="I71" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3558,10 +3620,10 @@
       <c r="B72" s="7">
         <v>46051</v>
       </c>
-      <c r="C72" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D72" s="22">
+      <c r="C72" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D72" s="21">
         <v>136469438</v>
       </c>
       <c r="E72" s="17">
@@ -3570,13 +3632,13 @@
       <c r="F72" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G72" s="67" t="s">
+      <c r="G72" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H72" s="46" t="s">
+      <c r="H72" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I72" s="44">
+      <c r="I72" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3587,10 +3649,10 @@
       <c r="B73" s="7">
         <v>46051</v>
       </c>
-      <c r="C73" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D73" s="22">
+      <c r="C73" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D73" s="21">
         <v>136472331</v>
       </c>
       <c r="E73" s="17">
@@ -3599,13 +3661,13 @@
       <c r="F73" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G73" s="67" t="s">
+      <c r="G73" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H73" s="46" t="s">
+      <c r="H73" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I73" s="44">
+      <c r="I73" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3616,10 +3678,10 @@
       <c r="B74" s="7">
         <v>46051</v>
       </c>
-      <c r="C74" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D74" s="22">
+      <c r="C74" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D74" s="21">
         <v>136472778</v>
       </c>
       <c r="E74" s="17">
@@ -3628,13 +3690,13 @@
       <c r="F74" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G74" s="67" t="s">
+      <c r="G74" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H74" s="46" t="s">
+      <c r="H74" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I74" s="44">
+      <c r="I74" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3645,10 +3707,10 @@
       <c r="B75" s="7">
         <v>46052</v>
       </c>
-      <c r="C75" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D75" s="22">
+      <c r="C75" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D75" s="21">
         <v>136479528</v>
       </c>
       <c r="E75" s="17">
@@ -3657,13 +3719,13 @@
       <c r="F75" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G75" s="67" t="s">
+      <c r="G75" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H75" s="46" t="s">
+      <c r="H75" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I75" s="44">
+      <c r="I75" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3674,10 +3736,10 @@
       <c r="B76" s="7">
         <v>46056</v>
       </c>
-      <c r="C76" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D76" s="22">
+      <c r="C76" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D76" s="21">
         <v>136525845</v>
       </c>
       <c r="E76" s="17">
@@ -3686,13 +3748,13 @@
       <c r="F76" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G76" s="67" t="s">
+      <c r="G76" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H76" s="46" t="s">
+      <c r="H76" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="I76" s="44">
+      <c r="I76" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -3703,10 +3765,10 @@
       <c r="B77" s="7">
         <v>46051</v>
       </c>
-      <c r="C77" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D77" s="22">
+      <c r="C77" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D77" s="21">
         <v>136482268</v>
       </c>
       <c r="E77" s="17">
@@ -3715,13 +3777,13 @@
       <c r="F77" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G77" s="67" t="s">
+      <c r="G77" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H77" s="46" t="s">
+      <c r="H77" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I77" s="44">
+      <c r="I77" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3732,10 +3794,10 @@
       <c r="B78" s="7">
         <v>46052</v>
       </c>
-      <c r="C78" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D78" s="22">
+      <c r="C78" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D78" s="21">
         <v>136482553</v>
       </c>
       <c r="E78" s="17">
@@ -3744,13 +3806,13 @@
       <c r="F78" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="67" t="s">
+      <c r="G78" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H78" s="46" t="s">
+      <c r="H78" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I78" s="44">
+      <c r="I78" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3761,10 +3823,10 @@
       <c r="B79" s="7">
         <v>46051</v>
       </c>
-      <c r="C79" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D79" s="22">
+      <c r="C79" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D79" s="21">
         <v>136483031</v>
       </c>
       <c r="E79" s="17">
@@ -3773,13 +3835,13 @@
       <c r="F79" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G79" s="67" t="s">
+      <c r="G79" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H79" s="46" t="s">
+      <c r="H79" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I79" s="44">
+      <c r="I79" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -3790,10 +3852,10 @@
       <c r="B80" s="7">
         <v>46052</v>
       </c>
-      <c r="C80" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D80" s="22">
+      <c r="C80" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D80" s="21">
         <v>136484642</v>
       </c>
       <c r="E80" s="17">
@@ -3802,13 +3864,13 @@
       <c r="F80" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G80" s="67" t="s">
+      <c r="G80" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H80" s="46" t="s">
+      <c r="H80" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I80" s="44">
+      <c r="I80" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3819,10 +3881,10 @@
       <c r="B81" s="7">
         <v>46052</v>
       </c>
-      <c r="C81" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D81" s="22">
+      <c r="C81" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D81" s="21">
         <v>136484917</v>
       </c>
       <c r="E81" s="17">
@@ -3831,13 +3893,13 @@
       <c r="F81" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G81" s="67" t="s">
+      <c r="G81" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H81" s="46" t="s">
+      <c r="H81" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I81" s="44">
+      <c r="I81" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3848,10 +3910,10 @@
       <c r="B82" s="7">
         <v>46052</v>
       </c>
-      <c r="C82" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D82" s="22">
+      <c r="C82" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D82" s="21">
         <v>136485282</v>
       </c>
       <c r="E82" s="17">
@@ -3860,13 +3922,13 @@
       <c r="F82" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G82" s="67" t="s">
+      <c r="G82" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H82" s="46" t="s">
+      <c r="H82" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I82" s="44">
+      <c r="I82" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3877,10 +3939,10 @@
       <c r="B83" s="7">
         <v>46052</v>
       </c>
-      <c r="C83" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D83" s="22">
+      <c r="C83" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D83" s="21">
         <v>136485305</v>
       </c>
       <c r="E83" s="17">
@@ -3889,13 +3951,13 @@
       <c r="F83" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G83" s="67" t="s">
+      <c r="G83" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H83" s="46" t="s">
+      <c r="H83" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I83" s="44">
+      <c r="I83" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3906,10 +3968,10 @@
       <c r="B84" s="7">
         <v>46052</v>
       </c>
-      <c r="C84" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D84" s="22">
+      <c r="C84" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D84" s="21">
         <v>136487849</v>
       </c>
       <c r="E84" s="17">
@@ -3918,13 +3980,13 @@
       <c r="F84" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G84" s="67" t="s">
+      <c r="G84" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H84" s="46" t="s">
+      <c r="H84" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I84" s="44">
+      <c r="I84" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3935,10 +3997,10 @@
       <c r="B85" s="7">
         <v>46052</v>
       </c>
-      <c r="C85" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D85" s="22">
+      <c r="C85" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D85" s="21">
         <v>136487918</v>
       </c>
       <c r="E85" s="17">
@@ -3947,13 +4009,13 @@
       <c r="F85" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G85" s="67" t="s">
+      <c r="G85" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H85" s="46" t="s">
+      <c r="H85" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I85" s="44">
+      <c r="I85" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3964,10 +4026,10 @@
       <c r="B86" s="7">
         <v>46052</v>
       </c>
-      <c r="C86" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D86" s="22">
+      <c r="C86" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D86" s="21">
         <v>136488238</v>
       </c>
       <c r="E86" s="17">
@@ -3976,13 +4038,13 @@
       <c r="F86" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G86" s="67" t="s">
+      <c r="G86" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H86" s="46" t="s">
+      <c r="H86" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I86" s="44">
+      <c r="I86" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -3993,10 +4055,10 @@
       <c r="B87" s="7">
         <v>46052</v>
       </c>
-      <c r="C87" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D87" s="22">
+      <c r="C87" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D87" s="21">
         <v>136490067</v>
       </c>
       <c r="E87" s="17">
@@ -4005,13 +4067,13 @@
       <c r="F87" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G87" s="67" t="s">
+      <c r="G87" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H87" s="46" t="s">
+      <c r="H87" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I87" s="44">
+      <c r="I87" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4022,10 +4084,10 @@
       <c r="B88" s="7">
         <v>46052</v>
       </c>
-      <c r="C88" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D88" s="22">
+      <c r="C88" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D88" s="21">
         <v>136490793</v>
       </c>
       <c r="E88" s="17">
@@ -4034,13 +4096,13 @@
       <c r="F88" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G88" s="67" t="s">
+      <c r="G88" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H88" s="46" t="s">
+      <c r="H88" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I88" s="44">
+      <c r="I88" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4051,10 +4113,10 @@
       <c r="B89" s="7">
         <v>46052</v>
       </c>
-      <c r="C89" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D89" s="22">
+      <c r="C89" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D89" s="21">
         <v>136491557</v>
       </c>
       <c r="E89" s="17">
@@ -4063,13 +4125,13 @@
       <c r="F89" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G89" s="67" t="s">
+      <c r="G89" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H89" s="46" t="s">
+      <c r="H89" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I89" s="44">
+      <c r="I89" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4080,10 +4142,10 @@
       <c r="B90" s="7">
         <v>46052</v>
       </c>
-      <c r="C90" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D90" s="22">
+      <c r="C90" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D90" s="21">
         <v>136492002</v>
       </c>
       <c r="E90" s="17">
@@ -4092,13 +4154,13 @@
       <c r="F90" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G90" s="67" t="s">
+      <c r="G90" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H90" s="46" t="s">
+      <c r="H90" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I90" s="44">
+      <c r="I90" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4109,10 +4171,10 @@
       <c r="B91" s="7">
         <v>46052</v>
       </c>
-      <c r="C91" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D91" s="22">
+      <c r="C91" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D91" s="21">
         <v>136493107</v>
       </c>
       <c r="E91" s="17">
@@ -4121,13 +4183,13 @@
       <c r="F91" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G91" s="67" t="s">
+      <c r="G91" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H91" s="46" t="s">
+      <c r="H91" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I91" s="44">
+      <c r="I91" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4138,10 +4200,10 @@
       <c r="B92" s="7">
         <v>46052</v>
       </c>
-      <c r="C92" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D92" s="22">
+      <c r="C92" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D92" s="21">
         <v>136493127</v>
       </c>
       <c r="E92" s="17">
@@ -4150,13 +4212,13 @@
       <c r="F92" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G92" s="67" t="s">
+      <c r="G92" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H92" s="46" t="s">
+      <c r="H92" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I92" s="44">
+      <c r="I92" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4167,10 +4229,10 @@
       <c r="B93" s="7">
         <v>46052</v>
       </c>
-      <c r="C93" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D93" s="22">
+      <c r="C93" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D93" s="21">
         <v>136493169</v>
       </c>
       <c r="E93" s="17">
@@ -4179,13 +4241,13 @@
       <c r="F93" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G93" s="67" t="s">
+      <c r="G93" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H93" s="45" t="s">
+      <c r="H93" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I93" s="44">
+      <c r="I93" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4196,10 +4258,10 @@
       <c r="B94" s="7">
         <v>46052</v>
       </c>
-      <c r="C94" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D94" s="22">
+      <c r="C94" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D94" s="21">
         <v>136493285</v>
       </c>
       <c r="E94" s="17">
@@ -4208,13 +4270,13 @@
       <c r="F94" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G94" s="67" t="s">
+      <c r="G94" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H94" s="45" t="s">
+      <c r="H94" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I94" s="44">
+      <c r="I94" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4225,10 +4287,10 @@
       <c r="B95" s="7">
         <v>46052</v>
       </c>
-      <c r="C95" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D95" s="22">
+      <c r="C95" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D95" s="21">
         <v>136493306</v>
       </c>
       <c r="E95" s="17">
@@ -4237,13 +4299,13 @@
       <c r="F95" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G95" s="67" t="s">
+      <c r="G95" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H95" s="45" t="s">
+      <c r="H95" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I95" s="44">
+      <c r="I95" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4254,10 +4316,10 @@
       <c r="B96" s="7">
         <v>46052</v>
       </c>
-      <c r="C96" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D96" s="22">
+      <c r="C96" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D96" s="21">
         <v>136493892</v>
       </c>
       <c r="E96" s="17">
@@ -4266,13 +4328,13 @@
       <c r="F96" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G96" s="67" t="s">
+      <c r="G96" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H96" s="45" t="s">
+      <c r="H96" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I96" s="44">
+      <c r="I96" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4283,10 +4345,10 @@
       <c r="B97" s="7">
         <v>46052</v>
       </c>
-      <c r="C97" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D97" s="22">
+      <c r="C97" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D97" s="21">
         <v>136494260</v>
       </c>
       <c r="E97" s="17">
@@ -4295,13 +4357,13 @@
       <c r="F97" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G97" s="67" t="s">
+      <c r="G97" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H97" s="45" t="s">
+      <c r="H97" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I97" s="44">
+      <c r="I97" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4312,10 +4374,10 @@
       <c r="B98" s="7">
         <v>46052</v>
       </c>
-      <c r="C98" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D98" s="22">
+      <c r="C98" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D98" s="21">
         <v>136494819</v>
       </c>
       <c r="E98" s="17">
@@ -4324,13 +4386,13 @@
       <c r="F98" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G98" s="67" t="s">
+      <c r="G98" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H98" s="45" t="s">
+      <c r="H98" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I98" s="44">
+      <c r="I98" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4341,10 +4403,10 @@
       <c r="B99" s="7">
         <v>46052</v>
       </c>
-      <c r="C99" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D99" s="22">
+      <c r="C99" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D99" s="21">
         <v>136495125</v>
       </c>
       <c r="E99" s="17">
@@ -4353,13 +4415,13 @@
       <c r="F99" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G99" s="67" t="s">
+      <c r="G99" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H99" s="45" t="s">
+      <c r="H99" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I99" s="44">
+      <c r="I99" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -4370,10 +4432,10 @@
       <c r="B100" s="7">
         <v>46052</v>
       </c>
-      <c r="C100" s="25">
-        <v>46062</v>
-      </c>
-      <c r="D100" s="22">
+      <c r="C100" s="23">
+        <v>46062</v>
+      </c>
+      <c r="D100" s="21">
         <v>136496179</v>
       </c>
       <c r="E100" s="17">
@@ -4382,71 +4444,71 @@
       <c r="F100" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G100" s="67" t="s">
+      <c r="G100" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="45" t="s">
+      <c r="H100" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I100" s="44">
+      <c r="I100" s="42">
         <v>46052</v>
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B101" s="71">
+      <c r="A101" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="63">
         <v>46052</v>
       </c>
-      <c r="C101" s="72">
-        <v>46062</v>
-      </c>
-      <c r="D101" s="73">
+      <c r="C101" s="64">
+        <v>46062</v>
+      </c>
+      <c r="D101" s="65">
         <v>136495243</v>
       </c>
-      <c r="E101" s="61">
+      <c r="E101" s="57">
         <v>3450236625</v>
       </c>
-      <c r="F101" s="62" t="s">
+      <c r="F101" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="G101" s="74" t="s">
+      <c r="G101" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="H101" s="75" t="s">
+      <c r="H101" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="I101" s="48">
+      <c r="I101" s="46">
         <v>46052</v>
       </c>
     </row>
     <row r="102" spans="1:9" s="12" customFormat="1">
-      <c r="A102" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B102" s="44">
+      <c r="A102" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="42">
         <v>46058</v>
       </c>
-      <c r="C102" s="44">
-        <v>46062</v>
-      </c>
-      <c r="D102" s="22" t="s">
+      <c r="C102" s="42">
+        <v>46062</v>
+      </c>
+      <c r="D102" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="E102" s="68">
+      <c r="E102" s="60">
         <v>3450242609</v>
       </c>
-      <c r="F102" s="69" t="s">
+      <c r="F102" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="G102" s="42" t="s">
+      <c r="G102" s="40" t="s">
         <v>132</v>
       </c>
       <c r="H102" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I102" s="44"/>
+      <c r="I102" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4476,67 +4538,67 @@
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="40.28515625" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="53">
+      <c r="A2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="51">
         <v>46051</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="52">
         <v>46063</v>
       </c>
-      <c r="D2" s="80">
+      <c r="D2" s="21">
         <v>136466416</v>
       </c>
       <c r="E2" s="17">
         <v>3450234315</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="56">
+      <c r="I2" s="53">
         <v>46051</v>
       </c>
     </row>
@@ -4547,25 +4609,25 @@
       <c r="B3" s="7">
         <v>46057</v>
       </c>
-      <c r="C3" s="54">
+      <c r="C3" s="52">
         <v>46063</v>
       </c>
-      <c r="D3" s="80">
+      <c r="D3" s="21">
         <v>136544694</v>
       </c>
       <c r="E3" s="17">
         <v>3450239804</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4576,25 +4638,25 @@
       <c r="B4" s="7">
         <v>46057</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="52">
         <v>46063</v>
       </c>
-      <c r="D4" s="80">
+      <c r="D4" s="21">
         <v>136546740</v>
       </c>
       <c r="E4" s="17">
         <v>3450239969</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="82" t="s">
+      <c r="H4" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4605,25 +4667,25 @@
       <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="52">
         <v>46063</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="21">
         <v>136556983</v>
       </c>
       <c r="E5" s="17">
         <v>3450241168</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -4634,25 +4696,25 @@
       <c r="B6" s="7">
         <v>46057</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="52">
         <v>46063</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="21">
         <v>136549649</v>
       </c>
       <c r="E6" s="17">
         <v>3450240387</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4663,25 +4725,25 @@
       <c r="B7" s="7">
         <v>46057</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="52">
         <v>46063</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="21">
         <v>136545020</v>
       </c>
       <c r="E7" s="17">
         <v>3450239815</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4692,25 +4754,25 @@
       <c r="B8" s="7">
         <v>46057</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="52">
         <v>46063</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="21">
         <v>136550615</v>
       </c>
       <c r="E8" s="17">
         <v>3450240519</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4721,25 +4783,25 @@
       <c r="B9" s="7">
         <v>46057</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="52">
         <v>46063</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="21">
         <v>136554112</v>
       </c>
       <c r="E9" s="17">
         <v>3450240882</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="67" t="s">
+      <c r="G9" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="82" t="s">
+      <c r="H9" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -4750,25 +4812,25 @@
       <c r="B10" s="7">
         <v>46057</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="52">
         <v>46063</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="21">
         <v>136547307</v>
       </c>
       <c r="E10" s="17">
         <v>3450240013</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="82" t="s">
+      <c r="H10" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4779,25 +4841,25 @@
       <c r="B11" s="7">
         <v>46060</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="52">
         <v>46063</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="21">
         <v>136577555</v>
       </c>
       <c r="E11" s="17">
         <v>3450242940</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="67" t="s">
+      <c r="G11" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="82" t="s">
+      <c r="H11" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -4808,25 +4870,25 @@
       <c r="B12" s="7">
         <v>46058</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="52">
         <v>46063</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="21">
         <v>136574106</v>
       </c>
       <c r="E12" s="17">
         <v>3450242532</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="82" t="s">
+      <c r="H12" s="72" t="s">
         <v>150</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="42">
         <v>46063</v>
       </c>
     </row>
@@ -4837,25 +4899,25 @@
       <c r="B13" s="7">
         <v>46058</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="52">
         <v>46063</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="21">
         <v>136569897</v>
       </c>
       <c r="E13" s="17">
         <v>3450241718</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="67" t="s">
+      <c r="G13" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="82" t="s">
+      <c r="H13" s="72" t="s">
         <v>152</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="42">
         <v>46058</v>
       </c>
     </row>
@@ -4866,25 +4928,25 @@
       <c r="B14" s="7">
         <v>46059</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="52">
         <v>46063</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="21">
         <v>136590604</v>
       </c>
       <c r="E14" s="17">
         <v>3450243478</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="82" t="s">
+      <c r="H14" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -4895,25 +4957,25 @@
       <c r="B15" s="7">
         <v>46059</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="52">
         <v>46063</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="21">
         <v>136605541</v>
       </c>
       <c r="E15" s="17">
         <v>3450244699</v>
       </c>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G15" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="82" t="s">
+      <c r="H15" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -4924,25 +4986,25 @@
       <c r="B16" s="7">
         <v>46066</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="52">
         <v>46063</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="21">
         <v>136589134</v>
       </c>
       <c r="E16" s="17">
         <v>3450243379</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="67" t="s">
+      <c r="G16" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="84" t="s">
+      <c r="H16" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -4953,25 +5015,25 @@
       <c r="B17" s="7">
         <v>46057</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="52">
         <v>46063</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="21">
         <v>136551257</v>
       </c>
       <c r="E17" s="17">
         <v>3450240585</v>
       </c>
-      <c r="F17" s="76" t="s">
+      <c r="F17" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="82" t="s">
+      <c r="H17" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -4982,25 +5044,25 @@
       <c r="B18" s="7">
         <v>46049</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="52">
         <v>46063</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="21">
         <v>136432160</v>
       </c>
       <c r="E18" s="17">
         <v>3450231510</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G18" s="67" t="s">
+      <c r="G18" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="84" t="s">
+      <c r="H18" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="42">
         <v>46051</v>
       </c>
     </row>
@@ -5011,25 +5073,25 @@
       <c r="B19" s="7">
         <v>46057</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="52">
         <v>46063</v>
       </c>
-      <c r="D19" s="80">
+      <c r="D19" s="21">
         <v>136556297</v>
       </c>
       <c r="E19" s="17">
         <v>3450241080</v>
       </c>
-      <c r="F19" s="76" t="s">
+      <c r="F19" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="67" t="s">
+      <c r="G19" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="82" t="s">
+      <c r="H19" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -5040,25 +5102,25 @@
       <c r="B20" s="7">
         <v>46057</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="52">
         <v>46063</v>
       </c>
-      <c r="D20" s="80">
+      <c r="D20" s="21">
         <v>136548776</v>
       </c>
       <c r="E20" s="17">
         <v>3450240244</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G20" s="67" t="s">
+      <c r="G20" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="82" t="s">
+      <c r="H20" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -5069,25 +5131,25 @@
       <c r="B21" s="7">
         <v>46063</v>
       </c>
-      <c r="C21" s="54">
+      <c r="C21" s="52">
         <v>46063</v>
       </c>
-      <c r="D21" s="80">
+      <c r="D21" s="21">
         <v>136463403</v>
       </c>
       <c r="E21" s="17">
         <v>3450233897</v>
       </c>
-      <c r="F21" s="76" t="s">
+      <c r="F21" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="G21" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H21" s="82" t="s">
+      <c r="H21" s="72" t="s">
         <v>163</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="42">
         <v>46059</v>
       </c>
     </row>
@@ -5098,25 +5160,25 @@
       <c r="B22" s="7">
         <v>46057</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="52">
         <v>46063</v>
       </c>
-      <c r="D22" s="80">
+      <c r="D22" s="21">
         <v>136549076</v>
       </c>
       <c r="E22" s="17">
         <v>3450240288</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="G22" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="82" t="s">
+      <c r="H22" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="42">
         <v>46057</v>
       </c>
     </row>
@@ -5127,25 +5189,25 @@
       <c r="B23" s="7">
         <v>46056</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="52">
         <v>46063</v>
       </c>
-      <c r="D23" s="80">
+      <c r="D23" s="21">
         <v>136526134</v>
       </c>
       <c r="E23" s="17">
         <v>3450238451</v>
       </c>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="82" t="s">
+      <c r="H23" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -5156,25 +5218,25 @@
       <c r="B24" s="7">
         <v>46055</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="52">
         <v>46063</v>
       </c>
-      <c r="D24" s="80">
+      <c r="D24" s="21">
         <v>136513461</v>
       </c>
       <c r="E24" s="17">
         <v>3450237615</v>
       </c>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="82" t="s">
+      <c r="H24" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="42">
         <v>46055</v>
       </c>
     </row>
@@ -5185,25 +5247,25 @@
       <c r="B25" s="7">
         <v>46059</v>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="52">
         <v>46063</v>
       </c>
-      <c r="D25" s="80">
+      <c r="D25" s="21">
         <v>136580070</v>
       </c>
       <c r="E25" s="17">
         <v>3450243170</v>
       </c>
-      <c r="F25" s="76" t="s">
+      <c r="F25" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="82" t="s">
+      <c r="H25" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -5214,25 +5276,25 @@
       <c r="B26" s="7">
         <v>46056</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="52">
         <v>46063</v>
       </c>
-      <c r="D26" s="80">
+      <c r="D26" s="21">
         <v>136524183</v>
       </c>
       <c r="E26" s="17">
         <v>3450238275</v>
       </c>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="82" t="s">
+      <c r="H26" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="42">
         <v>46056</v>
       </c>
     </row>
@@ -5243,25 +5305,25 @@
       <c r="B27" s="7">
         <v>46055</v>
       </c>
-      <c r="C27" s="54">
+      <c r="C27" s="52">
         <v>46063</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="21">
         <v>136500753</v>
       </c>
       <c r="E27" s="17">
         <v>3450236966</v>
       </c>
-      <c r="F27" s="76" t="s">
+      <c r="F27" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="G27" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H27" s="82" t="s">
+      <c r="H27" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -5272,25 +5334,25 @@
       <c r="B28" s="7">
         <v>46055</v>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="52">
         <v>46063</v>
       </c>
-      <c r="D28" s="80">
+      <c r="D28" s="21">
         <v>136512866</v>
       </c>
       <c r="E28" s="17">
         <v>3450237582</v>
       </c>
-      <c r="F28" s="76" t="s">
+      <c r="F28" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G28" s="67" t="s">
+      <c r="G28" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="82" t="s">
+      <c r="H28" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="42">
         <v>46062</v>
       </c>
     </row>
@@ -5301,25 +5363,25 @@
       <c r="B29" s="7">
         <v>46053</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="52">
         <v>46063</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="21">
         <v>136498050</v>
       </c>
       <c r="E29" s="17">
         <v>3450236834</v>
       </c>
-      <c r="F29" s="76" t="s">
+      <c r="F29" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="G29" s="67" t="s">
+      <c r="G29" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="82" t="s">
+      <c r="H29" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="42">
         <v>46053</v>
       </c>
     </row>
@@ -5330,25 +5392,25 @@
       <c r="B30" s="7">
         <v>46052</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="52">
         <v>46063</v>
       </c>
-      <c r="D30" s="80">
+      <c r="D30" s="21">
         <v>136499606</v>
       </c>
       <c r="E30" s="17">
         <v>3450236284</v>
       </c>
-      <c r="F30" s="76" t="s">
+      <c r="F30" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="67" t="s">
+      <c r="G30" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="82" t="s">
+      <c r="H30" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="42">
         <v>46052</v>
       </c>
     </row>
@@ -5359,38 +5421,54 @@
       <c r="B31" s="7">
         <v>46052</v>
       </c>
-      <c r="C31" s="54">
+      <c r="C31" s="52">
         <v>46063</v>
       </c>
-      <c r="D31" s="80">
+      <c r="D31" s="21">
         <v>136499685</v>
       </c>
       <c r="E31" s="17">
         <v>3450235734</v>
       </c>
-      <c r="F31" s="76" t="s">
+      <c r="F31" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="G31" s="67" t="s">
+      <c r="G31" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="82" t="s">
+      <c r="H31" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="48">
+      <c r="I31" s="46">
         <v>46052</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="44"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46063</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450246261</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="I32" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -5399,7 +5477,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G32" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
@@ -5412,17 +5490,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="26" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5450,7 +5529,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5458,472 +5537,697 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="54">
+        <v>46050</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46064</v>
+      </c>
+      <c r="D2" s="76">
+        <v>136455879</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450233480</v>
+      </c>
+      <c r="F2" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" s="42">
+        <v>46052</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="54">
+        <v>46056</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D3" s="76">
+        <v>136524492</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450238308</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="42">
+        <v>46056</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="54">
+        <v>46057</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46066</v>
+      </c>
+      <c r="D4" s="76">
+        <v>136546937</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450239970</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="42">
+        <v>46057</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="54">
+        <v>46056</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46067</v>
+      </c>
+      <c r="D5" s="76">
+        <v>136543214</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450239155</v>
+      </c>
+      <c r="F5" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="42">
+        <v>46056</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="54">
+        <v>46048</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46068</v>
+      </c>
+      <c r="D6" s="76">
+        <v>136569445</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450230421</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="42">
+        <v>46048</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="54">
+        <v>46058</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46069</v>
+      </c>
+      <c r="D7" s="76">
+        <v>136571337</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450242125</v>
+      </c>
+      <c r="F7" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="54">
+        <v>46058</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46070</v>
+      </c>
+      <c r="D8" s="76">
+        <v>136572246</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450242268</v>
+      </c>
+      <c r="F8" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="54">
+        <v>46058</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46071</v>
+      </c>
+      <c r="D9" s="76">
+        <v>136514831</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450237780</v>
+      </c>
+      <c r="F9" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="54">
+        <v>46058</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46072</v>
+      </c>
+      <c r="D10" s="76">
+        <v>136576510</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450242796</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="54">
+        <v>46058</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46073</v>
+      </c>
+      <c r="D11" s="76">
+        <v>136569102</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450241399</v>
+      </c>
+      <c r="F11" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="54">
+        <v>46059</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46074</v>
+      </c>
+      <c r="D12" s="76">
+        <v>136590176</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450243467</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I12" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="54">
+        <v>46059</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46075</v>
+      </c>
+      <c r="D13" s="76">
+        <v>136595018</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450243918</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I13" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="54">
+        <v>46059</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46076</v>
+      </c>
+      <c r="D14" s="76">
+        <v>136601750</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450244391</v>
+      </c>
+      <c r="F14" s="75" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="54">
+        <v>46059</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46077</v>
+      </c>
+      <c r="D15" s="76">
+        <v>136601805</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450244402</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="54">
+        <v>46077</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46078</v>
+      </c>
+      <c r="D16" s="76">
+        <v>136636095</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450245194</v>
+      </c>
+      <c r="F16" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I16" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="54">
+        <v>46077</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46079</v>
+      </c>
+      <c r="D17" s="76">
+        <v>136639628</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450245414</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I17" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46062</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46080</v>
+      </c>
+      <c r="D18" s="76">
+        <v>136644047</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450245667</v>
+      </c>
+      <c r="F18" s="75" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I18" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46081</v>
+      </c>
+      <c r="D19" s="76">
+        <v>136694699</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450248516</v>
+      </c>
+      <c r="F19" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46082</v>
+      </c>
+      <c r="D20" s="76">
+        <v>136453696</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450233336</v>
+      </c>
+      <c r="F20" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="77" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="42">
+        <v>46052</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46077</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46083</v>
+      </c>
+      <c r="D21" s="76">
+        <v>136551234</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450240563</v>
+      </c>
+      <c r="F21" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46056</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46085</v>
+      </c>
+      <c r="D22" s="76">
+        <v>136547472</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450238462</v>
+      </c>
+      <c r="F22" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I22" s="42">
+        <v>46056</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46086</v>
+      </c>
+      <c r="D23" s="76">
+        <v>136700316</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450249000</v>
+      </c>
+      <c r="F23" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="G23" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46087</v>
+      </c>
+      <c r="D24" s="76">
+        <v>136704748</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450249473</v>
+      </c>
+      <c r="F24" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A25" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5978,40 +6282,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -6019,12 +6323,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -6032,12 +6336,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -6045,12 +6349,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -6058,12 +6362,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -6071,12 +6375,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -6084,12 +6388,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -6097,12 +6401,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -6110,12 +6414,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="24"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -6123,12 +6427,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -6136,12 +6440,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -6149,23 +6453,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -6176,7 +6480,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -6187,7 +6491,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -6198,7 +6502,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -6209,7 +6513,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -6628,63 +6932,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -7211,7 +7515,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -7223,232 +7527,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -7457,9 +7761,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -7468,9 +7772,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -7479,9 +7783,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -7490,9 +7794,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="27"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -7501,9 +7805,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -7514,7 +7818,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -7525,7 +7829,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -7536,7 +7840,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -7547,7 +7851,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -7558,7 +7862,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -7569,7 +7873,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -7580,7 +7884,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -7591,7 +7895,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -7602,7 +7906,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -7613,7 +7917,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -7624,7 +7928,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -7914,494 +8218,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="41"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="41"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="41"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="41"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="41"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="41"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="41"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="41"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="41"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="41"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="41"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="42"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="40"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="41"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="40"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="40"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="42"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="40"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="42"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="40"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="41"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="40"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="40"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="42"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="40"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="42"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="40"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -8437,6 +8741,56 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -8444,7 +8798,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-543955</_dlc_DocId>
@@ -8487,7 +8841,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8871,68 +9225,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89CB077A-CD73-4763-809F-ADD5BD328777}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{158B6020-25E3-47B3-841D-EC546666E6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{771B1234-74EB-4B4C-9F2C-3F2E78AF34B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="09.02" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'09.02'!$A$1:$I$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'11.02'!$G$25:$G$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="267">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -699,6 +700,191 @@
   </si>
   <si>
     <t xml:space="preserve">FRANCISCO JULIO MANSANO NETO                 </t>
+  </si>
+  <si>
+    <t>ADRIANA GONZALEZ PINHEIRO MACHADO DOURADO CPF 85889679791</t>
+  </si>
+  <si>
+    <t>NUP- Cancelamento 11.02.2026</t>
+  </si>
+  <si>
+    <t>DANIEL SANTOS SANTANA FREIRE  CPF 83858970549</t>
+  </si>
+  <si>
+    <t>WANDERSON TARCYSO ARAUJO COSTA CPF 10303829486</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>VANESSA EDITE MOCO CORREA SA CPF 14942580722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO PAULO DE CARVALHO ALMEIDA              </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGRID MARTINS QUINTES                       </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2025/2026 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).
+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARZIRIA FERREIRA DIAS MEDEIROS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO BATISTA DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t>IS não encontrada para a Versão/CódFipe/AnoMod.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERNADETH CORTESE                            </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 11.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CAROLINA BERTAZI DA SILVA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMA SANTANA ALMEIDA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIANE COELHO FERREIRA DA SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NELSON PIVELLO                               </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Motor e placa (Foto não enquadrada), Frente e lateral do motorista, Frente e lateral do passageiro (Foto não enquadrada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINO CANDIDO DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t>KM INDISPONIVEL ***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: DOCUMENTO NAO ENVIADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O PARAIBA MOVEIS OUTLET LTDA ME              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA REGINA TRIZOLIO PALAMITE              </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi (Local incorreto), Frente e lateral do motorista (Foto não enquadrada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROQUE ELOIR GONCALVES DA COSTA               </t>
+  </si>
+  <si>
+    <t>VISTORIA A FRUSTRAR COM FOTOS INCORRETAS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO RAIMUNDO DOS SANTOS PAZ              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PASSO CHASSI NÃO ENVIADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUBERLANDIO ABRANTES SARMENTO                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi, Frente e lateral do motorista e passageiro, Traseira e lateral do motorista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELE CONCEICAO DE SOUZA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGELITA FERNANDES OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTO FERREIRA DE ARAUJO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLENE BEZERRA GUEDES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS BRANDAO DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ANDERSON SOARES DE OLIVEIRA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO DE SOUZA                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J L LOCACOES TRANSPORTES E SERVICOS LTDA EPP </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Chassi - local incorreto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL ARAUJO MALFITANO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE FIUZA GASPARINI                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIENE VIEIRA DE CASTRO                      </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) TACIANE MARIA VIEIRA DE CASTRO DA SILVA, pois este não consta
+como condutor na apólice anterior.
+Neste caso estamos nesta d
+ata efetuando a recusa desta proposta. Orientamos transmitir um no
+vo processo como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DE ABREU BUENO                          </t>
+  </si>
+  <si>
+    <t>&gt;Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIA LINS GEMIR                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJAQUES DOS SANTOS SILVA                     </t>
+  </si>
+  <si>
+    <t>Apólice a renovar já utilizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J RACOES LTDA ME                             </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi, Documento do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALANA REGINA MIRA DE SOUZA AZEVEDO           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CHASSI, PAINEL.</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1200,11 +1386,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5490,7 +5696,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -5498,7 +5704,7 @@
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.5703125" customWidth="1"/>
+    <col min="6" max="6" width="66.7109375" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" style="22" customWidth="1"/>
@@ -5543,19 +5749,19 @@
       <c r="C2" s="23">
         <v>46064</v>
       </c>
-      <c r="D2" s="76">
+      <c r="D2" s="21">
         <v>136455879</v>
       </c>
       <c r="E2" s="17">
         <v>3450233480</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="11" t="s">
         <v>180</v>
       </c>
       <c r="G2" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="12" t="s">
         <v>181</v>
       </c>
       <c r="I2" s="42">
@@ -5572,13 +5778,13 @@
       <c r="C3" s="23">
         <v>46065</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="21">
         <v>136524492</v>
       </c>
       <c r="E3" s="17">
         <v>3450238308</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="11" t="s">
         <v>182</v>
       </c>
       <c r="G3" s="40" t="s">
@@ -5601,13 +5807,13 @@
       <c r="C4" s="23">
         <v>46066</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="21">
         <v>136546937</v>
       </c>
       <c r="E4" s="17">
         <v>3450239970</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="11" t="s">
         <v>184</v>
       </c>
       <c r="G4" s="40" t="s">
@@ -5630,13 +5836,13 @@
       <c r="C5" s="23">
         <v>46067</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="21">
         <v>136543214</v>
       </c>
       <c r="E5" s="17">
         <v>3450239155</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="11" t="s">
         <v>186</v>
       </c>
       <c r="G5" s="40" t="s">
@@ -5659,13 +5865,13 @@
       <c r="C6" s="23">
         <v>46068</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="21">
         <v>136569445</v>
       </c>
       <c r="E6" s="17">
         <v>3450230421</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="11" t="s">
         <v>188</v>
       </c>
       <c r="G6" s="40" t="s">
@@ -5688,13 +5894,13 @@
       <c r="C7" s="23">
         <v>46069</v>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="21">
         <v>136571337</v>
       </c>
       <c r="E7" s="17">
         <v>3450242125</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="11" t="s">
         <v>189</v>
       </c>
       <c r="G7" s="40" t="s">
@@ -5717,13 +5923,13 @@
       <c r="C8" s="23">
         <v>46070</v>
       </c>
-      <c r="D8" s="76">
+      <c r="D8" s="21">
         <v>136572246</v>
       </c>
       <c r="E8" s="17">
         <v>3450242268</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="11" t="s">
         <v>190</v>
       </c>
       <c r="G8" s="40" t="s">
@@ -5746,13 +5952,13 @@
       <c r="C9" s="23">
         <v>46071</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="21">
         <v>136514831</v>
       </c>
       <c r="E9" s="17">
         <v>3450237780</v>
       </c>
-      <c r="F9" s="75" t="s">
+      <c r="F9" s="11" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="40" t="s">
@@ -5775,13 +5981,13 @@
       <c r="C10" s="23">
         <v>46072</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="21">
         <v>136576510</v>
       </c>
       <c r="E10" s="17">
         <v>3450242796</v>
       </c>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="11" t="s">
         <v>193</v>
       </c>
       <c r="G10" s="56" t="s">
@@ -5804,13 +6010,13 @@
       <c r="C11" s="23">
         <v>46073</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="21">
         <v>136569102</v>
       </c>
       <c r="E11" s="17">
         <v>3450241399</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="11" t="s">
         <v>195</v>
       </c>
       <c r="G11" s="40" t="s">
@@ -5833,13 +6039,13 @@
       <c r="C12" s="23">
         <v>46074</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="21">
         <v>136590176</v>
       </c>
       <c r="E12" s="17">
         <v>3450243467</v>
       </c>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="11" t="s">
         <v>145</v>
       </c>
       <c r="G12" s="56" t="s">
@@ -5862,13 +6068,13 @@
       <c r="C13" s="23">
         <v>46075</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="21">
         <v>136595018</v>
       </c>
       <c r="E13" s="17">
         <v>3450243918</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="11" t="s">
         <v>197</v>
       </c>
       <c r="G13" s="40" t="s">
@@ -5891,13 +6097,13 @@
       <c r="C14" s="23">
         <v>46076</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="21">
         <v>136601750</v>
       </c>
       <c r="E14" s="17">
         <v>3450244391</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="11" t="s">
         <v>199</v>
       </c>
       <c r="G14" s="40" t="s">
@@ -5920,13 +6126,13 @@
       <c r="C15" s="23">
         <v>46077</v>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="21">
         <v>136601805</v>
       </c>
       <c r="E15" s="17">
         <v>3450244402</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="11" t="s">
         <v>201</v>
       </c>
       <c r="G15" s="56" t="s">
@@ -5949,13 +6155,13 @@
       <c r="C16" s="23">
         <v>46078</v>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="21">
         <v>136636095</v>
       </c>
       <c r="E16" s="17">
         <v>3450245194</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G16" s="40" t="s">
@@ -5978,13 +6184,13 @@
       <c r="C17" s="23">
         <v>46079</v>
       </c>
-      <c r="D17" s="76">
+      <c r="D17" s="21">
         <v>136639628</v>
       </c>
       <c r="E17" s="17">
         <v>3450245414</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G17" s="40" t="s">
@@ -6007,13 +6213,13 @@
       <c r="C18" s="23">
         <v>46080</v>
       </c>
-      <c r="D18" s="76">
+      <c r="D18" s="21">
         <v>136644047</v>
       </c>
       <c r="E18" s="17">
         <v>3450245667</v>
       </c>
-      <c r="F18" s="75" t="s">
+      <c r="F18" s="11" t="s">
         <v>204</v>
       </c>
       <c r="G18" s="40" t="s">
@@ -6036,13 +6242,13 @@
       <c r="C19" s="23">
         <v>46081</v>
       </c>
-      <c r="D19" s="76">
+      <c r="D19" s="21">
         <v>136694699</v>
       </c>
       <c r="E19" s="17">
         <v>3450248516</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="11" t="s">
         <v>205</v>
       </c>
       <c r="G19" s="40" t="s">
@@ -6065,19 +6271,19 @@
       <c r="C20" s="23">
         <v>46082</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="21">
         <v>136453696</v>
       </c>
       <c r="E20" s="17">
         <v>3450233336</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="11" t="s">
         <v>206</v>
       </c>
       <c r="G20" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="77" t="s">
+      <c r="H20" s="12" t="s">
         <v>72</v>
       </c>
       <c r="I20" s="42">
@@ -6094,13 +6300,13 @@
       <c r="C21" s="23">
         <v>46083</v>
       </c>
-      <c r="D21" s="76">
+      <c r="D21" s="21">
         <v>136551234</v>
       </c>
       <c r="E21" s="17">
         <v>3450240563</v>
       </c>
-      <c r="F21" s="75" t="s">
+      <c r="F21" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G21" s="40" t="s">
@@ -6123,13 +6329,13 @@
       <c r="C22" s="23">
         <v>46085</v>
       </c>
-      <c r="D22" s="76">
+      <c r="D22" s="21">
         <v>136547472</v>
       </c>
       <c r="E22" s="17">
         <v>3450238462</v>
       </c>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="11" t="s">
         <v>207</v>
       </c>
       <c r="G22" s="40" t="s">
@@ -6152,13 +6358,13 @@
       <c r="C23" s="23">
         <v>46086</v>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="21">
         <v>136700316</v>
       </c>
       <c r="E23" s="17">
         <v>3450249000</v>
       </c>
-      <c r="F23" s="75" t="s">
+      <c r="F23" s="11" t="s">
         <v>209</v>
       </c>
       <c r="G23" s="56" t="s">
@@ -6181,13 +6387,13 @@
       <c r="C24" s="23">
         <v>46087</v>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="21">
         <v>136704748</v>
       </c>
       <c r="E24" s="17">
         <v>3450249473</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="11" t="s">
         <v>210</v>
       </c>
       <c r="G24" s="56" t="s">
@@ -6201,15 +6407,102 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="42"/>
+      <c r="A25" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="63">
+        <v>46064</v>
+      </c>
+      <c r="C25" s="63">
+        <v>46064</v>
+      </c>
+      <c r="D25" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="57">
+        <v>3450249132</v>
+      </c>
+      <c r="F25" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="I25" s="46"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="42">
+        <v>46062</v>
+      </c>
+      <c r="C26" s="63">
+        <v>46064</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="78">
+        <v>3450246173</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="I26" s="42"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="12"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="42"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="12"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="42"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="12"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="42"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="12"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -6217,15 +6510,12 @@
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A25" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A26" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6235,11 +6525,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
@@ -6282,601 +6572,1007 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="23">
+        <v>46059</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="8">
+        <v>3450243533</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="23">
+        <v>46062</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="82">
+        <v>3450245601</v>
+      </c>
+      <c r="F3" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="22"/>
+      <c r="B4" s="23">
+        <v>46054</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D4" s="84">
+        <v>136465591</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450234250</v>
+      </c>
+      <c r="F4" s="79" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="42">
+        <v>46055</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="22"/>
+      <c r="B5" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D5" s="84">
+        <v>136474860</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450234898</v>
+      </c>
+      <c r="F5" s="79" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="85" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="42">
+        <v>46056</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="22"/>
+      <c r="B6" s="7">
+        <v>46051</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D6" s="84">
+        <v>136463642</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450233920</v>
+      </c>
+      <c r="F6" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="85" t="s">
+        <v>222</v>
+      </c>
+      <c r="I6" s="42">
+        <v>46057</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="22"/>
+      <c r="B7" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D7" s="84">
+        <v>136518849</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450238044</v>
+      </c>
+      <c r="F7" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="80" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="I7" s="42">
+        <v>46065</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="22"/>
+      <c r="B8" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D8" s="84">
+        <v>136553134</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450240750</v>
+      </c>
+      <c r="F8" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I8" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="22"/>
+      <c r="B9" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D9" s="84">
+        <v>136551076</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450240541</v>
+      </c>
+      <c r="F9" s="79" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" s="42">
+        <v>46057</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="22"/>
+      <c r="B10" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D10" s="84">
+        <v>136558474</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450241290</v>
+      </c>
+      <c r="F10" s="79" t="s">
+        <v>229</v>
+      </c>
+      <c r="G10" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="I10" s="42">
+        <v>46057</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="22"/>
+      <c r="B11" s="7">
+        <v>46060</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D11" s="84">
+        <v>136547735</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450240057</v>
+      </c>
+      <c r="F11" s="79" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="22"/>
+      <c r="B12" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D12" s="84">
+        <v>136576164</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450242774</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="G12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="83" t="s">
+        <v>232</v>
+      </c>
+      <c r="I12" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="22"/>
+      <c r="B13" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D13" s="84">
+        <v>136591578</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450241751</v>
+      </c>
+      <c r="F13" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="83" t="s">
+        <v>234</v>
+      </c>
+      <c r="I13" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="22"/>
+      <c r="B14" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D14" s="84">
+        <v>136593052</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450243665</v>
+      </c>
+      <c r="F14" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="I14" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="22"/>
+      <c r="B15" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D15" s="84">
+        <v>136597563</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450244127</v>
+      </c>
+      <c r="F15" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="83" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="22"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D16" s="84">
+        <v>136593973</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450243742</v>
+      </c>
+      <c r="F16" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="83" t="s">
+        <v>240</v>
+      </c>
+      <c r="I16" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="22"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D17" s="84">
+        <v>136595745</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450244017</v>
+      </c>
+      <c r="F17" s="79" t="s">
+        <v>241</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="22"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D18" s="84">
+        <v>136605571</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450244710</v>
+      </c>
+      <c r="F18" s="79" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="I18" s="42">
+        <v>46059</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="22"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46060</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D19" s="84">
+        <v>136615073</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450244974</v>
+      </c>
+      <c r="F19" s="79" t="s">
+        <v>245</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="42">
+        <v>46060</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="22"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D20" s="84">
+        <v>136648173</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450245931</v>
+      </c>
+      <c r="F20" s="79" t="s">
+        <v>246</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I20" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46067</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D21" s="84">
+        <v>136653408</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450246338</v>
+      </c>
+      <c r="F21" s="79" t="s">
+        <v>247</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D22" s="84">
+        <v>136651167</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450246129</v>
+      </c>
+      <c r="F22" s="79" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I22" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D23" s="84">
+        <v>136669032</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450246822</v>
+      </c>
+      <c r="F23" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D24" s="84">
+        <v>136689621</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450248362</v>
+      </c>
+      <c r="F24" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C25" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D25" s="84">
+        <v>136694836</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450248550</v>
+      </c>
+      <c r="F25" s="79" t="s">
+        <v>250</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I25" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C26" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D26" s="84">
+        <v>136699378</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450248890</v>
+      </c>
+      <c r="F26" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C27" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D27" s="84">
+        <v>136570057</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450241762</v>
+      </c>
+      <c r="F27" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="83" t="s">
+        <v>253</v>
+      </c>
+      <c r="I27" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46056</v>
+      </c>
+      <c r="C28" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D28" s="84">
+        <v>136528200</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450238748</v>
+      </c>
+      <c r="F28" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="42">
+        <v>46063</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46057</v>
+      </c>
+      <c r="C29" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D29" s="84">
+        <v>136541423</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450239650</v>
+      </c>
+      <c r="F29" s="79" t="s">
+        <v>255</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I29" s="42">
+        <v>46064</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46055</v>
+      </c>
+      <c r="C30" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D30" s="84">
+        <v>136515044</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450237824</v>
+      </c>
+      <c r="F30" s="79" t="s">
+        <v>256</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="85" t="s">
+        <v>257</v>
+      </c>
+      <c r="I30" s="42">
+        <v>46062</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C31" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D31" s="84">
+        <v>136491409</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450236086</v>
+      </c>
+      <c r="F31" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="85" t="s">
+        <v>259</v>
+      </c>
+      <c r="I31" s="42">
+        <v>46058</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C32" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D32" s="84">
+        <v>136494552</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450236537</v>
+      </c>
+      <c r="F32" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="I32" s="42">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C33" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D33" s="84">
+        <v>136726323</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450250639</v>
+      </c>
+      <c r="F33" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="I33" s="42">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C34" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D34" s="84">
+        <v>136604000</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450244567</v>
+      </c>
+      <c r="F34" s="79" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" s="83" t="s">
+        <v>264</v>
+      </c>
+      <c r="I34" s="42">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C35" s="23">
+        <v>46065</v>
+      </c>
+      <c r="D35" s="84">
+        <v>136588781</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450243368</v>
+      </c>
+      <c r="F35" s="79" t="s">
+        <v>265</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="I35" s="42">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="8"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="14"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+      <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A35" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
-      <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8740,6 +9436,58 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-543955</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-543955</Url>
+      <Description>QAFFA7D2F2TC-2102087286-543955</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -8789,61 +9537,9 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-543955</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-543955</Url>
-      <Description>QAFFA7D2F2TC-2102087286-543955</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="f74e7f1d23a4a8b5c60f47e38d6dc018">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ad25b0159bf36a646e631d72af1d742f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -8893,12 +9589,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -8907,12 +9603,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -8995,7 +9691,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -9014,7 +9710,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -9047,7 +9743,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -9135,8 +9831,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -9226,7 +9922,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9234,9 +9930,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89CB077A-CD73-4763-809F-ADD5BD328777}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C742AA00-4EF0-4FF4-ABE6-62ADAD4FABAA}"/>
 </file>